--- a/2026/BELTRAN 34/Mayo/Mayo BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Mayo/Mayo BELTRAN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELTRAN 34\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7763FB0B-36EA-45C4-B54C-D60B89A0E54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9D5456-9417-4174-A122-81EEA9FC7213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$98</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="134">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -369,27 +374,9 @@
     <t>Yamila</t>
   </si>
   <si>
-    <t>Transf 25/04</t>
-  </si>
-  <si>
     <t>Ascensores Contessi - Mantenimiento de ascensores</t>
   </si>
   <si>
-    <t>Transf 06/04</t>
-  </si>
-  <si>
-    <t>Debito 07/04</t>
-  </si>
-  <si>
-    <t>Transf 13/04</t>
-  </si>
-  <si>
-    <t>Distribuidora Barbiero -  compra de materiales arreglo tablero de bomba</t>
-  </si>
-  <si>
-    <t>Facundo adelanto mano de obra</t>
-  </si>
-  <si>
     <t>Mariana Hebe Romeo</t>
   </si>
   <si>
@@ -405,24 +392,9 @@
     <t>VTO 18/06</t>
   </si>
   <si>
-    <t>Honorarios administracion - ABRIL</t>
-  </si>
-  <si>
-    <t>Ferreteria La primavera - Material de construccion</t>
-  </si>
-  <si>
-    <t>Ferreteria V&amp;A - Material electrico</t>
-  </si>
-  <si>
-    <t>Transf 05/05</t>
-  </si>
-  <si>
     <t>Transf 06/05</t>
   </si>
   <si>
-    <t>Reparaciones heredia - Adelanto: - Resta $110.000</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
@@ -435,7 +407,34 @@
     <t>Ascensores Contessi - Provision y cambio de contacto de puerta exterior del 2do piso</t>
   </si>
   <si>
-    <t>Destapacion</t>
+    <t>Copias de llaves - Cerrajeria EFE ELE</t>
+  </si>
+  <si>
+    <t>Debito 04/05</t>
+  </si>
+  <si>
+    <t>Sra. Abogada - Karina Iconomopulos - Envio de notificaciones deuda</t>
+  </si>
+  <si>
+    <t>Mes de Abril</t>
+  </si>
+  <si>
+    <t>Reparaciones heredia - Instalacion electrica de la sala de maquinas - 4 termicas (una para cada bomba) e instalacion de tomas para bombas - Adicional para bomba de succion, luz de emergencia y tomas. Dicha instalacion se hizo de forma exterior y a una altura segura debido a que la sala suele inundarse. Su utilizaron materiales de PVC. Se coloco una puesta a tierra individual para tablero y disyuntor idividual en el tablero principal para la sala de maquinas y alimencacion.</t>
+  </si>
+  <si>
+    <t>Destapacion Aysa Pago en efectivo - 18/5</t>
+  </si>
+  <si>
+    <t>Ascensores Contessi - Cuota 3/3 de provision y colocacion de dos barreras multihaz a la cabina del ascensor</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se adueda Abril y Mayo ($170.000)</t>
+  </si>
+  <si>
+    <t>Debito 12/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -451,7 +450,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -744,6 +743,13 @@
       <sz val="10"/>
       <name val="Arial1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -1454,7 +1460,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1484,7 +1490,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="17" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1573,7 +1578,6 @@
     </xf>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1611,12 +1615,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1638,7 +1640,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1662,6 +1663,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1689,6 +1697,18 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1704,9 +1724,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1737,16 +1754,11 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="43" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="43" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -1856,9 +1868,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1896,9 +1908,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1931,9 +1943,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1966,9 +1995,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2142,112 +2188,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L97"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L98"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="78"/>
+      <c r="B1" s="77"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-    </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1">
-      <c r="A3" s="79" t="s">
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
+      <c r="A3" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="155" t="s">
+      <c r="A4" s="153" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="155"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
+      <c r="B4" s="153"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="155"/>
-      <c r="B5" s="155"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
+      <c r="A5" s="153"/>
+      <c r="B5" s="153"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="155"/>
-      <c r="B6" s="155"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
+      <c r="A6" s="153"/>
+      <c r="B6" s="153"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="155"/>
-      <c r="B7" s="155"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
+      <c r="A7" s="153"/>
+      <c r="B7" s="153"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="163" t="s">
-        <v>124</v>
+      <c r="B9" s="161" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="163"/>
+      <c r="B10" s="161"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="163"/>
+      <c r="B11" s="161"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="158" t="s">
+      <c r="A14" s="156" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="158"/>
-      <c r="C14" s="158"/>
-      <c r="D14" s="158"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="158"/>
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
+      <c r="A15" s="156"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="158"/>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
+      <c r="A16" s="156"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="158"/>
-      <c r="B17" s="158"/>
-      <c r="C17" s="158"/>
-      <c r="D17" s="158"/>
+      <c r="A17" s="156"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="156"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1"/>
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1"/>
     <row r="21" spans="1:7">
       <c r="A21" s="6" t="s">
         <v>21</v>
@@ -2266,60 +2312,62 @@
       <c r="G22" s="22"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="123">
-        <v>0</v>
-      </c>
-      <c r="D23" s="55"/>
+      <c r="B23" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="183">
+        <v>192000</v>
+      </c>
+      <c r="D23" s="54"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="124" t="s">
+      <c r="A24" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="124"/>
-      <c r="C24" s="77">
+      <c r="B24" s="120"/>
+      <c r="C24" s="76">
         <f>SUM(C23:C23)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="56"/>
+        <v>192000</v>
+      </c>
+      <c r="D24" s="55"/>
     </row>
     <row r="25" spans="1:7" ht="0.6" customHeight="1">
-      <c r="A25" s="55"/>
-      <c r="B25" s="55"/>
-      <c r="C25" s="92"/>
-      <c r="D25" s="81"/>
+      <c r="A25" s="54"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="91"/>
+      <c r="D25" s="80"/>
     </row>
     <row r="26" spans="1:7" hidden="1">
-      <c r="A26" s="55"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="81"/>
+      <c r="A26" s="54"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="80"/>
     </row>
     <row r="27" spans="1:7" hidden="1">
-      <c r="A27" s="55"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="81"/>
+      <c r="A27" s="54"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="80"/>
     </row>
     <row r="28" spans="1:7" hidden="1">
-      <c r="A28" s="55"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="81"/>
+      <c r="A28" s="54"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="80"/>
     </row>
     <row r="29" spans="1:7" hidden="1">
-      <c r="A29" s="124" t="s">
+      <c r="A29" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="125"/>
+      <c r="B29" s="121"/>
       <c r="C29" s="28">
         <f>SUM(C25:C28)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="56"/>
+      <c r="D29" s="55"/>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="A30" s="14" t="s">
@@ -2327,9 +2375,9 @@
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="10"/>
-      <c r="D30" s="57">
+      <c r="D30" s="56">
         <f>C24+C29</f>
-        <v>0</v>
+        <v>192000</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -2340,32 +2388,30 @@
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="16"/>
-      <c r="D31" s="58"/>
+      <c r="D31" s="57"/>
       <c r="F31" s="9"/>
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A32" s="107" t="s">
-        <v>125</v>
-      </c>
-      <c r="B32" s="126"/>
-      <c r="C32" s="92">
-        <v>73700</v>
-      </c>
-      <c r="D32" s="90" t="s">
-        <v>117</v>
-      </c>
+      <c r="A32" s="105" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="122"/>
+      <c r="C32" s="91">
+        <v>0</v>
+      </c>
+      <c r="D32" s="89"/>
       <c r="F32" s="22"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1">
+    <row r="33" spans="1:6" ht="15.75" thickBot="1">
       <c r="A33" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="19"/>
-      <c r="D33" s="57">
+      <c r="D33" s="56">
         <f>SUM(C32:C32)</f>
-        <v>73700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5" customHeight="1">
@@ -2374,27 +2420,27 @@
       </c>
       <c r="B34" s="14"/>
       <c r="C34" s="17"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="33"/>
     </row>
     <row r="35" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A35" s="156" t="s">
+      <c r="A35" s="154" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="157"/>
-      <c r="C35" s="94">
+      <c r="B35" s="155"/>
+      <c r="C35" s="181">
         <v>168183</v>
       </c>
-      <c r="D35" s="89" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1">
+      <c r="D35" s="88" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1">
       <c r="A36" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="19"/>
-      <c r="D36" s="59">
+      <c r="D36" s="58">
         <f>SUM(C35:C35)</f>
         <v>168183</v>
       </c>
@@ -2403,58 +2449,58 @@
       <c r="A37" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="127"/>
+      <c r="B37" s="123"/>
       <c r="C37" s="20"/>
-      <c r="D37" s="60"/>
+      <c r="D37" s="59"/>
     </row>
     <row r="38" spans="1:6" hidden="1">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="55" t="s">
+      <c r="B38" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="95"/>
-      <c r="D38" s="89"/>
-      <c r="F38" s="83"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="88"/>
+      <c r="F38" s="82"/>
     </row>
     <row r="39" spans="1:6" hidden="1">
-      <c r="A39" s="55" t="s">
+      <c r="A39" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="55" t="s">
+      <c r="B39" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="96"/>
-      <c r="D39" s="89"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="88"/>
     </row>
     <row r="40" spans="1:6" hidden="1">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="B40" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="C40" s="96"/>
-      <c r="D40" s="89"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="88"/>
     </row>
     <row r="41" spans="1:6" hidden="1">
-      <c r="A41" s="55" t="s">
+      <c r="A41" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="96"/>
-      <c r="D41" s="88"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="87"/>
     </row>
     <row r="42" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1">
       <c r="A42" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="127"/>
+      <c r="B42" s="123"/>
       <c r="C42" s="21"/>
-      <c r="D42" s="59">
+      <c r="D42" s="58">
         <f>SUM(C38:C41)</f>
         <v>0</v>
       </c>
@@ -2463,489 +2509,502 @@
       <c r="A43" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="127"/>
+      <c r="B43" s="123"/>
       <c r="C43" s="20"/>
-      <c r="D43" s="60"/>
+      <c r="D43" s="59"/>
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A44" s="69" t="s">
+      <c r="A44" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="183">
+      <c r="B44" s="54"/>
+      <c r="C44" s="152">
         <v>61000.42</v>
       </c>
-      <c r="D44" s="87" t="s">
-        <v>133</v>
+      <c r="D44" s="86" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A45" s="55" t="s">
+      <c r="A45" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="B45" s="55"/>
-      <c r="C45" s="183">
+      <c r="B45" s="54"/>
+      <c r="C45" s="152">
+        <v>418590.24</v>
+      </c>
+      <c r="D45" s="86" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A46" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="54"/>
+      <c r="C46" s="152">
         <v>396294.49</v>
       </c>
-      <c r="D45" s="87" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1">
-      <c r="A46" s="14" t="s">
+      <c r="D46" s="86" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A47" s="14" t="s">
         <v>3</v>
-      </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="59">
-        <f>SUM(C44:C45)</f>
-        <v>457294.91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1">
-      <c r="A47" s="13" t="s">
-        <v>31</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="19"/>
-      <c r="D47" s="62"/>
-    </row>
-    <row r="48" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A48" s="156" t="s">
-        <v>114</v>
-      </c>
-      <c r="B48" s="157"/>
-      <c r="C48" s="183">
+      <c r="D47" s="58">
+        <f>SUM(C44:C46)</f>
+        <v>875885.14999999991</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A48" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48" s="14"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="61"/>
+    </row>
+    <row r="49" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A49" s="154" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" s="155"/>
+      <c r="C49" s="152">
         <f>105000+3547.5</f>
         <v>108547.5</v>
       </c>
-      <c r="D48" s="85" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1">
-      <c r="A49" s="156" t="s">
-        <v>134</v>
-      </c>
-      <c r="B49" s="157"/>
-      <c r="C49" s="183">
+      <c r="D49" s="84" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30" customHeight="1">
+      <c r="A50" s="154" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="155"/>
+      <c r="C50" s="152">
         <v>90000</v>
       </c>
-      <c r="D49" s="85" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A50" s="156" t="s">
+      <c r="D50" s="84" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" customHeight="1">
+      <c r="A51" s="154" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="157"/>
-      <c r="C50" s="183">
-        <v>350000</v>
-      </c>
-      <c r="D50" s="85" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A51" s="153" t="s">
-        <v>135</v>
-      </c>
-      <c r="B51" s="154"/>
-      <c r="C51" s="183">
+      <c r="B51" s="155"/>
+      <c r="C51" s="152">
+        <v>387000</v>
+      </c>
+      <c r="D51" s="84" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A52" s="150" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="151"/>
+      <c r="C52" s="152">
+        <v>20000</v>
+      </c>
+      <c r="D52" s="84"/>
+    </row>
+    <row r="53" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A53" s="148" t="s">
+        <v>129</v>
+      </c>
+      <c r="B53" s="149"/>
+      <c r="C53" s="152">
         <v>60000</v>
       </c>
-      <c r="D51" s="85"/>
-    </row>
-    <row r="52" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A52" s="153" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" s="154"/>
-      <c r="C52" s="183">
+      <c r="D53" s="84"/>
+    </row>
+    <row r="54" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A54" s="148" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="149"/>
+      <c r="C54" s="152">
         <v>43200</v>
       </c>
-      <c r="D52" s="85" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A53" s="156" t="s">
-        <v>126</v>
-      </c>
-      <c r="B53" s="157"/>
-      <c r="C53" s="183">
-        <v>28000</v>
-      </c>
-      <c r="D53" s="85" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A54" s="156" t="s">
-        <v>127</v>
-      </c>
-      <c r="B54" s="157"/>
-      <c r="C54" s="183">
-        <v>18000</v>
-      </c>
-      <c r="D54" s="85" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1">
-      <c r="A55" s="14" t="s">
+      <c r="D54" s="84" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A55" s="150" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="151"/>
+      <c r="C55" s="152">
+        <v>36900</v>
+      </c>
+      <c r="D55" s="84" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A56" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="64">
-        <f>SUM(C48:C54)</f>
-        <v>697747.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1">
-      <c r="A56" s="13" t="s">
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="63">
+        <f>SUM(C49:C55)</f>
+        <v>745647.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A57" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B56" s="128"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="62"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="55" t="s">
+      <c r="B57" s="124"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="61"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="B57" s="55"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="65"/>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="55" t="s">
+      <c r="B58" s="54"/>
+      <c r="C58" s="96"/>
+      <c r="D58" s="64"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="B58" s="55"/>
-      <c r="C58" s="96">
+      <c r="B59" s="54"/>
+      <c r="C59" s="94">
         <v>25055.13</v>
       </c>
-      <c r="D58" s="63"/>
-    </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1">
-      <c r="A59" s="129" t="s">
+      <c r="D59" s="62"/>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A60" s="125" t="s">
         <v>29</v>
       </c>
-      <c r="B59" s="129"/>
-      <c r="C59" s="66"/>
-      <c r="D59" s="59">
-        <f>SUM(C57:C58)</f>
+      <c r="B60" s="125"/>
+      <c r="C60" s="65"/>
+      <c r="D60" s="58">
+        <f>SUM(C58:C59)</f>
         <v>25055.13</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1">
-      <c r="A60" s="55"/>
-      <c r="B60" s="55"/>
-      <c r="C60" s="55"/>
-      <c r="D60" s="67"/>
-    </row>
-    <row r="61" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A61" s="160" t="s">
-        <v>123</v>
-      </c>
-      <c r="B61" s="161"/>
-      <c r="C61" s="162"/>
-      <c r="D61" s="68">
+    <row r="61" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A61" s="54"/>
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="66"/>
+    </row>
+    <row r="62" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A62" s="158" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" s="159"/>
+      <c r="C62" s="160"/>
+      <c r="D62" s="67">
         <f>1955000-1644013.49</f>
         <v>310986.51</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15" thickBot="1">
-      <c r="A62" s="130"/>
-      <c r="B62" s="69"/>
-      <c r="C62" s="69"/>
-      <c r="D62" s="70"/>
-      <c r="E62" s="24"/>
-    </row>
-    <row r="63" spans="1:6" ht="15" thickBot="1">
-      <c r="A63" s="131" t="s">
+    <row r="63" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A63" s="126"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="24"/>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A64" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="B63" s="132"/>
-      <c r="C63" s="71"/>
-      <c r="D63" s="72">
-        <f>(SUM(D25:D61))</f>
-        <v>1732967.0499999998</v>
-      </c>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="69"/>
-      <c r="B64" s="69"/>
-      <c r="C64" s="69"/>
-      <c r="D64" s="69"/>
-      <c r="F64" s="84"/>
-    </row>
-    <row r="65" spans="1:4" ht="15" thickBot="1">
-      <c r="A65" s="69"/>
-      <c r="B65" s="69"/>
-      <c r="C65" s="69"/>
-      <c r="D65" s="69"/>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="133" t="s">
+      <c r="B64" s="128"/>
+      <c r="C64" s="70"/>
+      <c r="D64" s="71">
+        <f>(SUM(D25:D62))</f>
+        <v>2317757.29</v>
+      </c>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="68"/>
+      <c r="B65" s="68"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="68"/>
+      <c r="F65" s="83"/>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A66" s="68"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68"/>
+      <c r="D66" s="68"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="B66" s="134"/>
-      <c r="C66" s="73"/>
-      <c r="D66" s="74"/>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="156" t="s">
-        <v>118</v>
-      </c>
-      <c r="B67" s="157"/>
-      <c r="C67" s="96">
-        <v>187647</v>
-      </c>
-      <c r="D67" s="85"/>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="156" t="s">
-        <v>119</v>
-      </c>
-      <c r="B68" s="157"/>
-      <c r="C68" s="96">
-        <v>112353</v>
-      </c>
-      <c r="D68" s="61"/>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="137"/>
-      <c r="B69" s="138"/>
-      <c r="C69" s="96"/>
-      <c r="D69" s="61"/>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="139"/>
-      <c r="B70" s="140"/>
-      <c r="C70" s="141"/>
-      <c r="D70" s="29">
-        <f>SUM(C67:C69)</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15" customHeight="1">
-      <c r="A71" s="69"/>
-      <c r="B71" s="69"/>
-      <c r="C71" s="69"/>
-    </row>
-    <row r="72" spans="1:4" hidden="1">
-      <c r="A72" s="69"/>
-      <c r="B72" s="69"/>
-      <c r="C72" s="69"/>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="142" t="s">
+      <c r="B67" s="130"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="73"/>
+    </row>
+    <row r="68" spans="1:6" ht="123.75" customHeight="1">
+      <c r="A68" s="154" t="s">
+        <v>128</v>
+      </c>
+      <c r="B68" s="155"/>
+      <c r="C68" s="152">
+        <v>460000</v>
+      </c>
+      <c r="D68" s="84"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" s="155"/>
+      <c r="C69" s="152">
+        <v>105000</v>
+      </c>
+      <c r="D69" s="60"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="133"/>
+      <c r="B70" s="134"/>
+      <c r="C70" s="94"/>
+      <c r="D70" s="60"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="125" t="s">
+        <v>29</v>
+      </c>
+      <c r="B71" s="135"/>
+      <c r="C71" s="136"/>
+      <c r="D71" s="182">
+        <f>SUM(C68:C70)</f>
+        <v>565000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15" customHeight="1">
+      <c r="A72" s="68"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="68"/>
+    </row>
+    <row r="73" spans="1:6" hidden="1">
+      <c r="A73" s="68"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="68"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="B73" s="142"/>
-      <c r="C73" s="143"/>
-      <c r="D73" s="91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="15" thickBot="1">
-      <c r="A74" s="69"/>
-      <c r="B74" s="69"/>
-      <c r="C74" s="69"/>
-    </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1">
-      <c r="A75" s="131" t="s">
+      <c r="B74" s="137"/>
+      <c r="C74" s="138"/>
+      <c r="D74" s="90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A75" s="68"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="68"/>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A76" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="B75" s="132"/>
-      <c r="C75" s="71"/>
-      <c r="D75" s="35">
-        <f>D70+D73</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1">
-      <c r="A76" s="69"/>
-      <c r="B76" s="69"/>
-      <c r="C76" s="69"/>
-    </row>
-    <row r="77" spans="1:4" ht="15" thickBot="1">
-      <c r="A77" s="144" t="s">
+      <c r="B76" s="128"/>
+      <c r="C76" s="70"/>
+      <c r="D76" s="34">
+        <f>D71+D74</f>
+        <v>565000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A77" s="68"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="68"/>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A78" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="B77" s="145">
-        <f>D63</f>
-        <v>1732967.0499999998</v>
-      </c>
-      <c r="C77" s="146"/>
-    </row>
-    <row r="78" spans="1:4" ht="15" thickBot="1">
-      <c r="A78" s="144" t="s">
+      <c r="B78" s="140">
+        <f>D64</f>
+        <v>2317757.29</v>
+      </c>
+      <c r="C78" s="141"/>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A79" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B78" s="145">
-        <f>D63-D61</f>
-        <v>1421980.5399999998</v>
-      </c>
-      <c r="C78" s="69"/>
-    </row>
-    <row r="79" spans="1:4" ht="15" thickBot="1">
-      <c r="A79" s="144" t="s">
+      <c r="B79" s="140">
+        <f>D64-D62</f>
+        <v>2006770.78</v>
+      </c>
+      <c r="C79" s="68"/>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A80" s="139" t="s">
         <v>37</v>
       </c>
-      <c r="B79" s="145">
-        <f>D75-D73</f>
-        <v>300000</v>
-      </c>
-      <c r="C79" s="69"/>
-    </row>
-    <row r="80" spans="1:4" ht="15" thickBot="1">
-      <c r="A80" s="144" t="s">
+      <c r="B80" s="140">
+        <f>D76-D74</f>
+        <v>565000</v>
+      </c>
+      <c r="C80" s="68"/>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A81" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="B80" s="145">
-        <f>D75</f>
-        <v>300000</v>
-      </c>
-      <c r="C80" s="69"/>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="69"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="69"/>
+      <c r="B81" s="140">
+        <f>D76</f>
+        <v>565000</v>
+      </c>
+      <c r="C81" s="68"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="69"/>
-      <c r="B82" s="69"/>
-      <c r="C82" s="69"/>
+      <c r="A82" s="68"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="68"/>
+      <c r="D82" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="69"/>
-      <c r="B83" s="69"/>
-      <c r="C83" s="69"/>
-    </row>
-    <row r="84" spans="1:4" ht="15" thickBot="1">
-      <c r="A84" s="147" t="s">
+      <c r="A83" s="68"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="68"/>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="68"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68"/>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A85" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="B84" s="148"/>
-      <c r="C84" s="69"/>
-    </row>
-    <row r="85" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A85" s="12" t="s">
+      <c r="B85" s="143"/>
+      <c r="C85" s="68"/>
+    </row>
+    <row r="86" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A86" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B85" s="149">
-        <v>420429.50999999978</v>
-      </c>
-      <c r="C85" s="69"/>
-    </row>
-    <row r="86" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A86" s="150" t="s">
+      <c r="B86" s="144">
+        <v>464169.03999999957</v>
+      </c>
+      <c r="C86" s="68"/>
+    </row>
+    <row r="87" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A87" s="145" t="s">
         <v>55</v>
       </c>
-      <c r="B86" s="63">
+      <c r="B87" s="62">
         <f>PRORRATEO!H24</f>
-        <v>1987753.0199999998</v>
-      </c>
-      <c r="C86" s="69"/>
-    </row>
-    <row r="87" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A87" s="150" t="s">
+        <v>1942758.8299999996</v>
+      </c>
+      <c r="C87" s="68"/>
+    </row>
+    <row r="88" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A88" s="145" t="s">
         <v>54</v>
       </c>
-      <c r="B87" s="63">
-        <f>B96</f>
-        <v>0</v>
-      </c>
-      <c r="C87" s="69"/>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="152" t="s">
+      <c r="B88" s="62">
+        <f>B97</f>
+        <v>0</v>
+      </c>
+      <c r="C88" s="68"/>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="B88" s="63">
-        <f>-B78</f>
-        <v>-1421980.5399999998</v>
-      </c>
-      <c r="C88" s="69"/>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="151" t="s">
+      <c r="B89" s="62">
+        <f>-B79</f>
+        <v>-2006770.78</v>
+      </c>
+      <c r="C89" s="68"/>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="B89" s="63">
-        <f>-(B79)</f>
-        <v>-300000</v>
-      </c>
-      <c r="C89" s="69"/>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="11" t="s">
+      <c r="B90" s="62">
+        <f>-(B80)</f>
+        <v>-565000</v>
+      </c>
+      <c r="C90" s="68"/>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B90" s="108">
-        <f>SUM(B85:B89)</f>
-        <v>686201.98999999953</v>
-      </c>
-      <c r="C90" s="136"/>
-    </row>
-    <row r="91" spans="1:4" ht="34.5" customHeight="1">
-      <c r="B91" s="22"/>
-      <c r="C91" s="24"/>
-      <c r="D91" s="136"/>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="159" t="s">
+      <c r="B91" s="106">
+        <f>SUM(B86:B90)</f>
+        <v>-164842.91000000085</v>
+      </c>
+      <c r="C91" s="132"/>
+    </row>
+    <row r="92" spans="1:4" ht="34.5" customHeight="1">
+      <c r="B92" s="22"/>
+      <c r="C92" s="24"/>
+      <c r="D92" s="132"/>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="157" t="s">
         <v>46</v>
       </c>
-      <c r="B92" s="159"/>
-    </row>
-    <row r="93" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A93" s="159"/>
-      <c r="B93" s="159"/>
-    </row>
-    <row r="94" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A94" s="75"/>
-      <c r="B94" s="18"/>
+      <c r="B93" s="157"/>
+    </row>
+    <row r="94" spans="1:4" ht="27.75" customHeight="1">
+      <c r="A94" s="157"/>
+      <c r="B94" s="157"/>
     </row>
     <row r="95" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A95" s="75"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="18"/>
     </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="25" t="s">
+    <row r="96" spans="1:4" ht="32.25" customHeight="1">
+      <c r="A96" s="74"/>
+      <c r="B96" s="18"/>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B96" s="76">
-        <f>SUM(B94:B95)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="12:12">
-      <c r="L97" s="4"/>
+      <c r="B97" s="75">
+        <f>SUM(B95:B96)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="L98" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A92:B93"/>
+    <mergeCell ref="A93:B94"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2956,194 +3015,194 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.9" customHeight="1">
-      <c r="A1" s="109"/>
-      <c r="B1" s="164" t="str">
+    <row r="1" spans="1:21" ht="12.95" customHeight="1">
+      <c r="A1" s="107"/>
+      <c r="B1" s="166" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="111"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="109"/>
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
-      <c r="A2" s="112"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="165"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113" t="s">
+      <c r="A2" s="110"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="167"/>
+      <c r="F2" s="167"/>
+      <c r="G2" s="167"/>
+      <c r="H2" s="167"/>
+      <c r="I2" s="167"/>
+      <c r="J2" s="167"/>
+      <c r="K2" s="167"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111" t="s">
         <v>4</v>
       </c>
       <c r="N2" s="3"/>
-      <c r="O2" s="121">
+      <c r="O2" s="118">
         <v>1955000</v>
       </c>
-      <c r="P2" s="114"/>
+      <c r="P2" s="112"/>
       <c r="Q2" s="9"/>
       <c r="R2">
         <v>1406361.51</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
-      <c r="A3" s="115"/>
-      <c r="B3" s="166"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116" t="s">
+      <c r="A3" s="113"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
+      <c r="G3" s="168"/>
+      <c r="H3" s="168"/>
+      <c r="I3" s="168"/>
+      <c r="J3" s="168"/>
+      <c r="K3" s="168"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="N3" s="117"/>
-      <c r="O3" s="122">
-        <v>0</v>
-      </c>
-      <c r="P3" s="118"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="119">
+        <v>0</v>
+      </c>
+      <c r="P3" s="116"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="177" t="s">
+      <c r="B4" s="178" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="178"/>
-      <c r="I4" s="178"/>
-      <c r="J4" s="178"/>
-      <c r="K4" s="178"/>
-      <c r="L4" s="178"/>
-      <c r="M4" s="178"/>
-      <c r="N4" s="178"/>
-      <c r="O4" s="178"/>
-      <c r="P4" s="179"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
+      <c r="L4" s="179"/>
+      <c r="M4" s="179"/>
+      <c r="N4" s="179"/>
+      <c r="O4" s="179"/>
+      <c r="P4" s="180"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="182" t="s">
+      <c r="B5" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="169" t="s">
+      <c r="C5" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="169" t="s">
+      <c r="D5" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="169" t="s">
+      <c r="E5" s="165" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="169" t="s">
+      <c r="F5" s="165" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="169" t="s">
+      <c r="G5" s="165" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="169" t="s">
+      <c r="H5" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="169" t="s">
+      <c r="I5" s="165" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="173" t="s">
+      <c r="J5" s="174" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="171" t="s">
+      <c r="K5" s="172" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="171" t="s">
+      <c r="L5" s="172" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="171" t="s">
+      <c r="M5" s="172" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="175" t="s">
+      <c r="N5" s="176" t="s">
         <v>51</v>
       </c>
-      <c r="O5" s="97" t="s">
+      <c r="O5" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="167" t="s">
+      <c r="P5" s="169" t="s">
         <v>49</v>
       </c>
       <c r="S5" s="24"/>
       <c r="T5" s="22"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="181"/>
-      <c r="B6" s="182"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="169"/>
-      <c r="E6" s="170"/>
-      <c r="F6" s="169"/>
-      <c r="G6" s="169"/>
-      <c r="H6" s="169"/>
-      <c r="I6" s="170"/>
-      <c r="J6" s="174"/>
-      <c r="K6" s="172"/>
-      <c r="L6" s="171"/>
-      <c r="M6" s="172"/>
-      <c r="N6" s="176"/>
-      <c r="O6" s="30" t="str">
+      <c r="A6" s="163"/>
+      <c r="B6" s="164"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="171"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="171"/>
+      <c r="J6" s="175"/>
+      <c r="K6" s="173"/>
+      <c r="L6" s="172"/>
+      <c r="M6" s="173"/>
+      <c r="N6" s="177"/>
+      <c r="O6" s="29" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="P6" s="167"/>
+      <c r="P6" s="169"/>
       <c r="S6" s="22">
         <v>65160</v>
       </c>
@@ -3159,50 +3218,50 @@
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="31">
         <v>1</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="36">
+      <c r="E7" s="31"/>
+      <c r="F7" s="35">
         <v>10.86</v>
       </c>
-      <c r="G7" s="37">
-        <v>3846496.01</v>
-      </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="40">
+      <c r="G7" s="36">
+        <v>4174204.01</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="39">
         <f>G7-H7</f>
-        <v>3846496.01</v>
-      </c>
-      <c r="K7" s="40">
+        <v>4174204.01</v>
+      </c>
+      <c r="K7" s="39">
         <f>IF(J7&gt;0,J7*3%,0)</f>
-        <v>115394.88029999999</v>
-      </c>
-      <c r="L7" s="41">
+        <v>125226.1203</v>
+      </c>
+      <c r="L7" s="40">
         <f>O$3*F7%</f>
         <v>0</v>
       </c>
-      <c r="M7" s="41">
+      <c r="M7" s="40">
         <f>O$2*F7%</f>
         <v>212312.99999999997</v>
       </c>
-      <c r="N7" s="42">
-        <v>0</v>
-      </c>
-      <c r="O7" s="43">
+      <c r="N7" s="41">
+        <v>0</v>
+      </c>
+      <c r="O7" s="42">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>4174204.01</v>
-      </c>
-      <c r="P7" s="44">
+        <v>4511743.01</v>
+      </c>
+      <c r="P7" s="43">
         <f t="shared" ref="P7:P23" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>4299430.01</v>
+        <v>4647095.01</v>
       </c>
       <c r="Q7" s="24">
         <v>0.01</v>
@@ -3222,52 +3281,52 @@
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="31">
         <v>2</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="36">
+      <c r="E8" s="32"/>
+      <c r="F8" s="35">
         <v>11.16</v>
       </c>
-      <c r="G8" s="37">
-        <v>215470.02</v>
-      </c>
-      <c r="H8" s="38">
-        <v>0</v>
-      </c>
-      <c r="I8" s="39"/>
-      <c r="J8" s="40">
+      <c r="G8" s="36">
+        <v>440112.02</v>
+      </c>
+      <c r="H8" s="184">
+        <v>233588.14</v>
+      </c>
+      <c r="I8" s="38"/>
+      <c r="J8" s="39">
         <f t="shared" ref="J8:J22" si="2">G8-H8</f>
-        <v>215470.02</v>
-      </c>
-      <c r="K8" s="40">
+        <v>206523.88</v>
+      </c>
+      <c r="K8" s="39">
         <f t="shared" ref="K8:K22" si="3">IF(J8&gt;0,J8*3%,0)</f>
-        <v>6464.1005999999998</v>
-      </c>
-      <c r="L8" s="41">
+        <v>6195.7164000000002</v>
+      </c>
+      <c r="L8" s="40">
         <f t="shared" ref="L8:L23" si="4">O$3*F8%</f>
         <v>0</v>
       </c>
-      <c r="M8" s="41">
+      <c r="M8" s="40">
         <f t="shared" ref="M8:M23" si="5">O$2*F8%</f>
         <v>218178</v>
       </c>
-      <c r="N8" s="42">
-        <v>0</v>
-      </c>
-      <c r="O8" s="43">
+      <c r="N8" s="41">
+        <v>0</v>
+      </c>
+      <c r="O8" s="42">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>440112.02</v>
-      </c>
-      <c r="P8" s="44">
+        <v>430898.02</v>
+      </c>
+      <c r="P8" s="43">
         <f t="shared" si="0"/>
-        <v>453315.02</v>
+        <v>443825.02</v>
       </c>
       <c r="Q8" s="24">
         <f>Q7+0.01</f>
@@ -3289,54 +3348,54 @@
       <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="86">
+      <c r="B9" s="85">
         <v>4</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="99" t="s">
+      <c r="D9" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="86" t="s">
+      <c r="E9" s="85" t="s">
         <v>108</v>
       </c>
-      <c r="F9" s="101">
+      <c r="F9" s="99">
         <v>6.95</v>
       </c>
-      <c r="G9" s="38">
-        <v>261156.03</v>
-      </c>
-      <c r="H9" s="38">
-        <v>85873</v>
-      </c>
-      <c r="I9" s="39"/>
-      <c r="J9" s="102">
+      <c r="G9" s="37">
+        <v>316414.03000000003</v>
+      </c>
+      <c r="H9" s="37">
+        <v>0</v>
+      </c>
+      <c r="I9" s="38"/>
+      <c r="J9" s="100">
         <f t="shared" si="2"/>
-        <v>175283.03</v>
-      </c>
-      <c r="K9" s="40">
+        <v>316414.03000000003</v>
+      </c>
+      <c r="K9" s="39">
         <f t="shared" si="3"/>
-        <v>5258.4908999999998</v>
-      </c>
-      <c r="L9" s="103">
+        <v>9492.420900000001</v>
+      </c>
+      <c r="L9" s="101">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="101">
         <f t="shared" si="5"/>
         <v>135872.5</v>
       </c>
-      <c r="N9" s="104">
-        <v>0</v>
-      </c>
-      <c r="O9" s="105">
+      <c r="N9" s="102">
+        <v>0</v>
+      </c>
+      <c r="O9" s="103">
         <f t="shared" ref="O9:O23" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>316414.03000000003</v>
-      </c>
-      <c r="P9" s="106">
+        <v>461779.03</v>
+      </c>
+      <c r="P9" s="104">
         <f t="shared" si="0"/>
-        <v>325906.03000000003</v>
+        <v>475632.03</v>
       </c>
       <c r="Q9" s="24">
         <f t="shared" ref="Q9:Q22" si="7">Q8+0.01</f>
@@ -3357,55 +3416,55 @@
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="31">
         <v>3</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="36">
+      <c r="E10" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="F10" s="35">
         <v>7.37</v>
       </c>
-      <c r="G10" s="37">
-        <v>148624.04</v>
-      </c>
-      <c r="H10" s="38">
-        <f>2211-H20+155000</f>
-        <v>146888.85999999999</v>
-      </c>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40">
+      <c r="G10" s="36">
+        <v>145871.04000000001</v>
+      </c>
+      <c r="H10" s="184">
+        <f>-H20+158000</f>
+        <v>147833.85999999999</v>
+      </c>
+      <c r="I10" s="38"/>
+      <c r="J10" s="39">
         <f t="shared" si="2"/>
-        <v>1735.1800000000221</v>
-      </c>
-      <c r="K10" s="40">
+        <v>-1962.8199999999779</v>
+      </c>
+      <c r="K10" s="39">
         <f t="shared" si="3"/>
-        <v>52.05540000000066</v>
-      </c>
-      <c r="L10" s="41">
+        <v>0</v>
+      </c>
+      <c r="L10" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M10" s="41">
+      <c r="M10" s="40">
         <f t="shared" si="5"/>
         <v>144083.5</v>
       </c>
-      <c r="N10" s="42">
-        <v>0</v>
-      </c>
-      <c r="O10" s="43">
+      <c r="N10" s="41">
+        <v>0</v>
+      </c>
+      <c r="O10" s="42">
         <f t="shared" si="6"/>
-        <v>145871.04000000001</v>
-      </c>
-      <c r="P10" s="44">
+        <v>142121.04</v>
+      </c>
+      <c r="P10" s="43">
         <f t="shared" si="0"/>
-        <v>150247.04000000001</v>
+        <v>146385.04</v>
       </c>
       <c r="Q10" s="24">
         <f t="shared" si="7"/>
@@ -3426,53 +3485,53 @@
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="31">
         <v>5</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="35">
         <v>10.68</v>
       </c>
-      <c r="G11" s="37">
-        <v>214308.05</v>
-      </c>
-      <c r="H11" s="38">
+      <c r="G11" s="36">
+        <v>215058.05</v>
+      </c>
+      <c r="H11" s="184">
         <f>G11</f>
-        <v>214308.05</v>
-      </c>
-      <c r="I11" s="39"/>
-      <c r="J11" s="40">
+        <v>215058.05</v>
+      </c>
+      <c r="I11" s="38"/>
+      <c r="J11" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="41">
+      <c r="L11" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M11" s="41">
+      <c r="M11" s="40">
         <f t="shared" si="5"/>
         <v>208793.99999999997</v>
       </c>
-      <c r="N11" s="42">
-        <v>0</v>
-      </c>
-      <c r="O11" s="43">
+      <c r="N11" s="41">
+        <v>0</v>
+      </c>
+      <c r="O11" s="42">
         <f t="shared" si="6"/>
         <v>208794.05</v>
       </c>
-      <c r="P11" s="44">
+      <c r="P11" s="43">
         <f t="shared" si="0"/>
         <v>215058.05</v>
       </c>
@@ -3495,54 +3554,55 @@
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="31">
         <v>7</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="35">
         <v>6.95</v>
       </c>
-      <c r="G12" s="37">
-        <v>137958.06</v>
-      </c>
-      <c r="H12" s="38">
-        <v>150069</v>
-      </c>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40">
+      <c r="G12" s="36">
+        <v>123762.06</v>
+      </c>
+      <c r="H12" s="184">
+        <f>145825-H22</f>
+        <v>123762.84</v>
+      </c>
+      <c r="I12" s="38"/>
+      <c r="J12" s="39">
         <f t="shared" si="2"/>
-        <v>-12110.940000000002</v>
-      </c>
-      <c r="K12" s="40">
+        <v>-0.77999999999883585</v>
+      </c>
+      <c r="K12" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L12" s="41">
+      <c r="L12" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="41">
+      <c r="M12" s="40">
         <f t="shared" si="5"/>
         <v>135872.5</v>
       </c>
-      <c r="N12" s="135">
-        <v>0</v>
-      </c>
-      <c r="O12" s="43">
+      <c r="N12" s="131">
+        <v>0</v>
+      </c>
+      <c r="O12" s="42">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>123762.06</v>
-      </c>
-      <c r="P12" s="44">
+        <v>135872.06</v>
+      </c>
+      <c r="P12" s="43">
         <f t="shared" si="0"/>
-        <v>127475.06</v>
+        <v>139948.06</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="7"/>
@@ -3563,53 +3623,53 @@
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="31">
         <v>6</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="86" t="s">
+      <c r="D13" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="35">
         <v>6.89</v>
       </c>
-      <c r="G13" s="37">
-        <v>136767.07</v>
-      </c>
-      <c r="H13" s="38">
+      <c r="G13" s="36">
+        <v>134700.07</v>
+      </c>
+      <c r="H13" s="184">
         <f>G13</f>
-        <v>136767.07</v>
-      </c>
-      <c r="I13" s="39"/>
-      <c r="J13" s="40">
+        <v>134700.07</v>
+      </c>
+      <c r="I13" s="38"/>
+      <c r="J13" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K13" s="40">
+      <c r="K13" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13" s="41">
+      <c r="L13" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M13" s="41">
+      <c r="M13" s="40">
         <f t="shared" si="5"/>
         <v>134699.5</v>
       </c>
-      <c r="N13" s="42">
-        <v>0</v>
-      </c>
-      <c r="O13" s="43">
+      <c r="N13" s="41">
+        <v>0</v>
+      </c>
+      <c r="O13" s="42">
         <f t="shared" si="6"/>
         <v>134700.07</v>
       </c>
-      <c r="P13" s="44">
+      <c r="P13" s="43">
         <f t="shared" si="0"/>
         <v>138741.07</v>
       </c>
@@ -3617,8 +3677,8 @@
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R13" s="84"/>
-      <c r="S13" s="119">
+      <c r="R13" s="83"/>
+      <c r="S13" s="117">
         <v>64080</v>
       </c>
       <c r="T13" s="22">
@@ -3633,54 +3693,55 @@
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="31">
         <v>8</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="35">
         <v>10.68</v>
       </c>
-      <c r="G14" s="37">
-        <v>211998.07999999999</v>
-      </c>
-      <c r="H14" s="38">
-        <v>218358.08</v>
-      </c>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40">
+      <c r="G14" s="36">
+        <v>202434.08</v>
+      </c>
+      <c r="H14" s="184">
+        <f>G14</f>
+        <v>202434.08</v>
+      </c>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39">
         <f t="shared" si="2"/>
-        <v>-6360</v>
-      </c>
-      <c r="K14" s="40">
+        <v>0</v>
+      </c>
+      <c r="K14" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L14" s="41">
+      <c r="L14" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M14" s="41">
+      <c r="M14" s="40">
         <f t="shared" si="5"/>
         <v>208793.99999999997</v>
       </c>
-      <c r="N14" s="42">
-        <v>0</v>
-      </c>
-      <c r="O14" s="43">
+      <c r="N14" s="41">
+        <v>0</v>
+      </c>
+      <c r="O14" s="42">
         <f t="shared" si="6"/>
-        <v>202434.08</v>
-      </c>
-      <c r="P14" s="44">
+        <v>208794.08</v>
+      </c>
+      <c r="P14" s="43">
         <f t="shared" si="0"/>
-        <v>208507.08</v>
+        <v>215058.08</v>
       </c>
       <c r="Q14" s="24">
         <f t="shared" si="7"/>
@@ -3701,54 +3762,54 @@
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="86">
+      <c r="B15" s="85">
         <v>10</v>
       </c>
-      <c r="C15" s="86" t="s">
+      <c r="C15" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="86" t="s">
+      <c r="D15" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="F15" s="101">
+      <c r="F15" s="99">
         <v>6.95</v>
       </c>
-      <c r="G15" s="38">
-        <v>1026398.09</v>
-      </c>
-      <c r="H15" s="120">
-        <f>135873+500000</f>
-        <v>635873</v>
-      </c>
-      <c r="I15" s="39"/>
-      <c r="J15" s="102">
+      <c r="G15" s="37">
+        <v>526398.09</v>
+      </c>
+      <c r="H15" s="185">
+        <f>135873+330000</f>
+        <v>465873</v>
+      </c>
+      <c r="I15" s="38"/>
+      <c r="J15" s="100">
         <f t="shared" si="2"/>
-        <v>390525.08999999997</v>
-      </c>
-      <c r="K15" s="102">
-        <v>0</v>
-      </c>
-      <c r="L15" s="103">
+        <v>60525.089999999967</v>
+      </c>
+      <c r="K15" s="100">
+        <v>0</v>
+      </c>
+      <c r="L15" s="101">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M15" s="103">
+      <c r="M15" s="101">
         <f t="shared" si="5"/>
         <v>135872.5</v>
       </c>
-      <c r="N15" s="104">
-        <v>0</v>
-      </c>
-      <c r="O15" s="105">
+      <c r="N15" s="102">
+        <v>0</v>
+      </c>
+      <c r="O15" s="103">
         <f t="shared" si="6"/>
-        <v>526398.09</v>
-      </c>
-      <c r="P15" s="106">
+        <v>196398.09</v>
+      </c>
+      <c r="P15" s="104">
         <f t="shared" si="0"/>
-        <v>542190.09</v>
+        <v>202290.09</v>
       </c>
       <c r="Q15" s="24">
         <f t="shared" si="7"/>
@@ -3769,53 +3830,53 @@
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="31">
         <v>9</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="35">
         <v>6.89</v>
       </c>
-      <c r="G16" s="37">
-        <v>136767.1</v>
-      </c>
-      <c r="H16" s="38">
-        <f>2067+134700</f>
-        <v>136767</v>
-      </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40">
+      <c r="G16" s="36">
+        <v>134700.1</v>
+      </c>
+      <c r="H16" s="184">
+        <f>134700.1</f>
+        <v>134700.1</v>
+      </c>
+      <c r="I16" s="38"/>
+      <c r="J16" s="39">
         <f t="shared" si="2"/>
-        <v>0.10000000000582077</v>
-      </c>
-      <c r="K16" s="40">
+        <v>0</v>
+      </c>
+      <c r="K16" s="39">
         <f t="shared" si="3"/>
-        <v>3.000000000174623E-3</v>
-      </c>
-      <c r="L16" s="41">
+        <v>0</v>
+      </c>
+      <c r="L16" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M16" s="41">
+      <c r="M16" s="40">
         <f t="shared" si="5"/>
         <v>134699.5</v>
       </c>
-      <c r="N16" s="42">
-        <v>0</v>
-      </c>
-      <c r="O16" s="43">
+      <c r="N16" s="41">
+        <v>0</v>
+      </c>
+      <c r="O16" s="42">
         <f t="shared" si="6"/>
         <v>134700.1</v>
       </c>
-      <c r="P16" s="44">
+      <c r="P16" s="43">
         <f t="shared" si="0"/>
         <v>138741.1</v>
       </c>
@@ -3824,7 +3885,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R16" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="S16" s="22">
         <v>71280</v>
@@ -3841,60 +3902,60 @@
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="31">
         <v>11</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="36">
+      <c r="E17" s="32"/>
+      <c r="F17" s="35">
         <v>11.88</v>
       </c>
-      <c r="G17" s="37">
-        <v>229836.11</v>
-      </c>
-      <c r="H17" s="38">
-        <f>162510.69+77386</f>
-        <v>239896.69</v>
-      </c>
-      <c r="I17" s="39"/>
-      <c r="J17" s="40">
+      <c r="G17" s="36">
+        <v>222193.11</v>
+      </c>
+      <c r="H17" s="184">
+        <f>232254.11-H21+10166.15</f>
+        <v>221892.11</v>
+      </c>
+      <c r="I17" s="38"/>
+      <c r="J17" s="39">
         <f t="shared" si="2"/>
-        <v>-10060.580000000016</v>
-      </c>
-      <c r="K17" s="40">
+        <v>301</v>
+      </c>
+      <c r="K17" s="39">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="41">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="L17" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M17" s="41">
+      <c r="M17" s="40">
         <f t="shared" si="5"/>
         <v>232254</v>
       </c>
-      <c r="N17" s="42">
-        <v>0</v>
-      </c>
-      <c r="O17" s="43">
+      <c r="N17" s="41">
+        <v>0</v>
+      </c>
+      <c r="O17" s="42">
         <f t="shared" si="6"/>
-        <v>222193.11</v>
-      </c>
-      <c r="P17" s="44">
+        <v>232564.11</v>
+      </c>
+      <c r="P17" s="43">
         <f t="shared" si="0"/>
-        <v>228859.11</v>
+        <v>239541.11</v>
       </c>
       <c r="Q17" s="24">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="R17" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="S17" s="22">
         <v>3420</v>
@@ -3911,52 +3972,52 @@
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="36">
+      <c r="E18" s="32"/>
+      <c r="F18" s="35">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G18" s="37">
-        <v>11315.12</v>
-      </c>
-      <c r="H18" s="38">
-        <v>0</v>
-      </c>
-      <c r="I18" s="39"/>
-      <c r="J18" s="40">
+      <c r="G18" s="36">
+        <v>22798.12</v>
+      </c>
+      <c r="H18" s="37">
+        <v>0</v>
+      </c>
+      <c r="I18" s="38"/>
+      <c r="J18" s="39">
         <f t="shared" si="2"/>
-        <v>11315.12</v>
-      </c>
-      <c r="K18" s="40">
+        <v>22798.12</v>
+      </c>
+      <c r="K18" s="39">
         <f t="shared" si="3"/>
-        <v>339.45359999999999</v>
-      </c>
-      <c r="L18" s="41">
+        <v>683.94359999999995</v>
+      </c>
+      <c r="L18" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M18" s="41">
+      <c r="M18" s="40">
         <f t="shared" si="5"/>
         <v>11143.499999999998</v>
       </c>
-      <c r="N18" s="42">
-        <v>0</v>
-      </c>
-      <c r="O18" s="43">
+      <c r="N18" s="41">
+        <v>0</v>
+      </c>
+      <c r="O18" s="42">
         <f t="shared" si="6"/>
-        <v>22798.12</v>
-      </c>
-      <c r="P18" s="44">
+        <v>34626.120000000003</v>
+      </c>
+      <c r="P18" s="43">
         <f t="shared" si="0"/>
-        <v>23482.12</v>
+        <v>35665.120000000003</v>
       </c>
       <c r="Q18" s="24">
         <f t="shared" si="7"/>
@@ -3977,52 +4038,52 @@
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="36">
+      <c r="E19" s="32"/>
+      <c r="F19" s="35">
         <v>0.52</v>
       </c>
-      <c r="G19" s="37">
-        <v>10060.129999999999</v>
-      </c>
-      <c r="H19" s="38">
-        <v>10362.129999999999</v>
-      </c>
-      <c r="I19" s="39"/>
-      <c r="J19" s="40">
+      <c r="G19" s="36">
+        <v>9864.1299999999992</v>
+      </c>
+      <c r="H19" s="184">
+        <v>10160.129999999999</v>
+      </c>
+      <c r="I19" s="38"/>
+      <c r="J19" s="39">
         <f t="shared" si="2"/>
-        <v>-302</v>
-      </c>
-      <c r="K19" s="40">
+        <v>-296</v>
+      </c>
+      <c r="K19" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L19" s="41">
+      <c r="L19" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M19" s="41">
+      <c r="M19" s="40">
         <f t="shared" si="5"/>
         <v>10166</v>
       </c>
-      <c r="N19" s="42">
-        <v>0</v>
-      </c>
-      <c r="O19" s="43">
+      <c r="N19" s="41">
+        <v>0</v>
+      </c>
+      <c r="O19" s="42">
         <f t="shared" si="6"/>
-        <v>9864.1299999999992</v>
-      </c>
-      <c r="P19" s="44">
+        <v>9870.1299999999992</v>
+      </c>
+      <c r="P19" s="43">
         <f t="shared" si="0"/>
-        <v>10160.129999999999</v>
+        <v>10166.129999999999</v>
       </c>
       <c r="Q19" s="24">
         <f t="shared" si="7"/>
@@ -4043,53 +4104,53 @@
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="35">
         <v>0.52</v>
       </c>
-      <c r="G20" s="37">
-        <v>10322.14</v>
-      </c>
-      <c r="H20" s="38">
+      <c r="G20" s="36">
+        <v>10166.14</v>
+      </c>
+      <c r="H20" s="184">
         <f>G20</f>
-        <v>10322.14</v>
-      </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="40">
+        <v>10166.14</v>
+      </c>
+      <c r="I20" s="38"/>
+      <c r="J20" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K20" s="40">
+      <c r="K20" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L20" s="41">
+      <c r="L20" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M20" s="41">
+      <c r="M20" s="40">
         <f t="shared" si="5"/>
         <v>10166</v>
       </c>
-      <c r="N20" s="42">
-        <v>0</v>
-      </c>
-      <c r="O20" s="43">
+      <c r="N20" s="41">
+        <v>0</v>
+      </c>
+      <c r="O20" s="42">
         <f t="shared" si="6"/>
         <v>10166.14</v>
       </c>
-      <c r="P20" s="44">
+      <c r="P20" s="43">
         <f t="shared" si="0"/>
         <v>10471.14</v>
       </c>
@@ -4112,52 +4173,53 @@
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="36">
+      <c r="E21" s="32"/>
+      <c r="F21" s="35">
         <v>0.52</v>
       </c>
-      <c r="G21" s="37">
-        <v>10060.15</v>
-      </c>
-      <c r="H21" s="38">
-        <v>0</v>
-      </c>
-      <c r="I21" s="39"/>
-      <c r="J21" s="40">
+      <c r="G21" s="36">
+        <v>20528.150000000001</v>
+      </c>
+      <c r="H21" s="184">
+        <f>G21</f>
+        <v>20528.150000000001</v>
+      </c>
+      <c r="I21" s="38"/>
+      <c r="J21" s="39">
         <f t="shared" si="2"/>
-        <v>10060.15</v>
-      </c>
-      <c r="K21" s="40">
+        <v>0</v>
+      </c>
+      <c r="K21" s="39">
         <f t="shared" si="3"/>
-        <v>301.80449999999996</v>
-      </c>
-      <c r="L21" s="41">
+        <v>0</v>
+      </c>
+      <c r="L21" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M21" s="41">
+      <c r="M21" s="40">
         <f t="shared" si="5"/>
         <v>10166</v>
       </c>
-      <c r="N21" s="42">
-        <v>0</v>
-      </c>
-      <c r="O21" s="43">
+      <c r="N21" s="41">
+        <v>0</v>
+      </c>
+      <c r="O21" s="42">
         <f t="shared" si="6"/>
-        <v>20528.150000000001</v>
-      </c>
-      <c r="P21" s="44">
+        <v>10166.15</v>
+      </c>
+      <c r="P21" s="43">
         <f t="shared" si="0"/>
-        <v>21144.15</v>
+        <v>10471.15</v>
       </c>
       <c r="Q21" s="24">
         <f t="shared" si="7"/>
@@ -4178,52 +4240,53 @@
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="32"/>
-      <c r="F22" s="36">
+      <c r="E22" s="31"/>
+      <c r="F22" s="35">
         <v>0.61</v>
       </c>
-      <c r="G22" s="37">
-        <v>12109.16</v>
-      </c>
-      <c r="H22" s="38">
-        <v>2268</v>
-      </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="40">
+      <c r="G22" s="36">
+        <v>22062.16</v>
+      </c>
+      <c r="H22" s="184">
+        <f>G22</f>
+        <v>22062.16</v>
+      </c>
+      <c r="I22" s="38"/>
+      <c r="J22" s="39">
         <f t="shared" si="2"/>
-        <v>9841.16</v>
-      </c>
-      <c r="K22" s="40">
+        <v>0</v>
+      </c>
+      <c r="K22" s="39">
         <f t="shared" si="3"/>
-        <v>295.23480000000001</v>
-      </c>
-      <c r="L22" s="41">
+        <v>0</v>
+      </c>
+      <c r="L22" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M22" s="41">
+      <c r="M22" s="40">
         <f t="shared" si="5"/>
         <v>11925.499999999998</v>
       </c>
-      <c r="N22" s="42">
-        <v>0</v>
-      </c>
-      <c r="O22" s="43">
+      <c r="N22" s="41">
+        <v>0</v>
+      </c>
+      <c r="O22" s="42">
         <f t="shared" si="6"/>
-        <v>22062.16</v>
-      </c>
-      <c r="P22" s="44">
+        <v>11926.16</v>
+      </c>
+      <c r="P22" s="43">
         <f t="shared" si="0"/>
-        <v>22724.16</v>
+        <v>12284.16</v>
       </c>
       <c r="Q22" s="24">
         <f t="shared" si="7"/>
@@ -4235,190 +4298,187 @@
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="45" t="s">
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="38" t="str">
+      <c r="H23" s="37" t="str">
         <f t="shared" ref="H23" si="8">G23</f>
         <v>162450.31</v>
       </c>
-      <c r="I23" s="46"/>
-      <c r="J23" s="47" t="e">
+      <c r="I23" s="45"/>
+      <c r="J23" s="46" t="e">
         <f t="shared" ref="J23" si="9">G23-H23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K23" s="40" t="e">
+      <c r="K23" s="39" t="e">
         <f t="shared" ref="K23" si="10">IF(J23&gt;0,J23*3%,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L23" s="41">
+      <c r="L23" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M23" s="48">
+      <c r="M23" s="47">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N23" s="49">
-        <v>0</v>
-      </c>
-      <c r="O23" s="43" t="e">
+      <c r="N23" s="48">
+        <v>0</v>
+      </c>
+      <c r="O23" s="42" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P23" s="44" t="e">
+      <c r="P23" s="43" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="53">
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="52">
         <f>SUM(F7:F23)</f>
         <v>99.999999999999972</v>
       </c>
       <c r="G24" s="27">
         <f>SUM(G7:G23)</f>
-        <v>6619645.3599999994</v>
-      </c>
-      <c r="H24" s="31">
+        <v>6721265.3599999994</v>
+      </c>
+      <c r="H24" s="30">
         <f>SUM(H7:H23)</f>
-        <v>1987753.0199999998</v>
-      </c>
-      <c r="I24" s="31">
+        <v>1942758.8299999996</v>
+      </c>
+      <c r="I24" s="30">
         <f>SUM(I7:I23)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31">
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30">
         <f>SUM(L7:L23)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="30">
         <f>SUM(M7:M23)</f>
         <v>1955000</v>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="30">
         <f>SUM(N7:N23)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="54">
+      <c r="O24" s="53">
         <f>SUM(O7:O22)</f>
-        <v>6715001.3599999994</v>
-      </c>
-      <c r="P24" s="54">
+        <v>6875118.3599999994</v>
+      </c>
+      <c r="P24" s="53">
         <f>SUM(P7:P22)</f>
-        <v>6916451.3599999994</v>
+        <v>7081372.3599999994</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="12.75" customHeight="1">
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
+      <c r="S25" s="24"/>
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
-    <row r="27" spans="1:21" ht="9" customHeight="1">
-      <c r="D27" s="168" t="s">
+    <row r="27" spans="1:21" ht="15" customHeight="1">
+      <c r="D27" s="170" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="168"/>
-      <c r="F27" s="168"/>
-      <c r="G27" s="168"/>
-      <c r="H27" s="168"/>
-      <c r="I27" s="168"/>
-      <c r="J27" s="168"/>
-      <c r="K27" s="168"/>
-      <c r="L27" s="168"/>
-      <c r="M27" s="168"/>
-      <c r="N27" s="168"/>
-      <c r="O27" s="168"/>
+      <c r="E27" s="170"/>
+      <c r="F27" s="170"/>
+      <c r="G27" s="170"/>
+      <c r="H27" s="170"/>
+      <c r="I27" s="170"/>
+      <c r="J27" s="170"/>
+      <c r="K27" s="170"/>
+      <c r="L27" s="170"/>
+      <c r="M27" s="170"/>
+      <c r="N27" s="170"/>
+      <c r="O27" s="170"/>
+      <c r="S27" s="22"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="168"/>
-      <c r="E28" s="168"/>
-      <c r="F28" s="168"/>
-      <c r="G28" s="168"/>
-      <c r="H28" s="168"/>
-      <c r="I28" s="168"/>
-      <c r="J28" s="168"/>
-      <c r="K28" s="168"/>
-      <c r="L28" s="168"/>
-      <c r="M28" s="168"/>
-      <c r="N28" s="168"/>
-      <c r="O28" s="168"/>
+      <c r="D28" s="170"/>
+      <c r="E28" s="170"/>
+      <c r="F28" s="170"/>
+      <c r="G28" s="170"/>
+      <c r="H28" s="170"/>
+      <c r="I28" s="170"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="170"/>
+      <c r="L28" s="170"/>
+      <c r="M28" s="170"/>
+      <c r="N28" s="170"/>
+      <c r="O28" s="170"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="168"/>
-      <c r="E29" s="168"/>
-      <c r="F29" s="168"/>
-      <c r="G29" s="168"/>
-      <c r="H29" s="168"/>
-      <c r="I29" s="168"/>
-      <c r="J29" s="168"/>
-      <c r="K29" s="168"/>
-      <c r="L29" s="168"/>
-      <c r="M29" s="168"/>
-      <c r="N29" s="168"/>
-      <c r="O29" s="168"/>
+      <c r="D29" s="170"/>
+      <c r="E29" s="170"/>
+      <c r="F29" s="170"/>
+      <c r="G29" s="170"/>
+      <c r="H29" s="170"/>
+      <c r="I29" s="170"/>
+      <c r="J29" s="170"/>
+      <c r="K29" s="170"/>
+      <c r="L29" s="170"/>
+      <c r="M29" s="170"/>
+      <c r="N29" s="170"/>
+      <c r="O29" s="170"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="168"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="168"/>
-      <c r="H30" s="168"/>
-      <c r="I30" s="168"/>
-      <c r="J30" s="168"/>
-      <c r="K30" s="168"/>
-      <c r="L30" s="168"/>
-      <c r="M30" s="168"/>
-      <c r="N30" s="168"/>
-      <c r="O30" s="168"/>
+      <c r="D30" s="170"/>
+      <c r="E30" s="170"/>
+      <c r="F30" s="170"/>
+      <c r="G30" s="170"/>
+      <c r="H30" s="170"/>
+      <c r="I30" s="170"/>
+      <c r="J30" s="170"/>
+      <c r="K30" s="170"/>
+      <c r="L30" s="170"/>
+      <c r="M30" s="170"/>
+      <c r="N30" s="170"/>
+      <c r="O30" s="170"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="168"/>
-      <c r="E31" s="168"/>
-      <c r="F31" s="168"/>
-      <c r="G31" s="168"/>
-      <c r="H31" s="168"/>
-      <c r="I31" s="168"/>
-      <c r="J31" s="168"/>
-      <c r="K31" s="168"/>
-      <c r="L31" s="168"/>
-      <c r="M31" s="168"/>
-      <c r="N31" s="168"/>
-      <c r="O31" s="168"/>
+      <c r="D31" s="170"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="170"/>
+      <c r="H31" s="170"/>
+      <c r="I31" s="170"/>
+      <c r="J31" s="170"/>
+      <c r="K31" s="170"/>
+      <c r="L31" s="170"/>
+      <c r="M31" s="170"/>
+      <c r="N31" s="170"/>
+      <c r="O31" s="170"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="168"/>
-      <c r="E32" s="168"/>
-      <c r="F32" s="168"/>
-      <c r="G32" s="168"/>
-      <c r="H32" s="168"/>
-      <c r="I32" s="168"/>
-      <c r="J32" s="168"/>
-      <c r="K32" s="168"/>
-      <c r="L32" s="168"/>
-      <c r="M32" s="168"/>
-      <c r="N32" s="168"/>
-      <c r="O32" s="168"/>
+      <c r="D32" s="170"/>
+      <c r="E32" s="170"/>
+      <c r="F32" s="170"/>
+      <c r="G32" s="170"/>
+      <c r="H32" s="170"/>
+      <c r="I32" s="170"/>
+      <c r="J32" s="170"/>
+      <c r="K32" s="170"/>
+      <c r="L32" s="170"/>
+      <c r="M32" s="170"/>
+      <c r="N32" s="170"/>
+      <c r="O32" s="170"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4432,6 +4492,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>

--- a/2026/BELTRAN 34/Mayo/Mayo BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Mayo/Mayo BELTRAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9D5456-9417-4174-A122-81EEA9FC7213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9A345A-8E43-4D9F-A806-9C95C1B009BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="135">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -431,10 +431,13 @@
     <t>Honorarios administracion - Se adueda Abril y Mayo ($170.000)</t>
   </si>
   <si>
-    <t>Debito 12/05</t>
-  </si>
-  <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>Pendiente para el cierre de Juni0 poner un AYSA de 418.590,24</t>
+  </si>
+  <si>
+    <t>Cobro erroneo arreglo de ascensor</t>
   </si>
 </sst>
 </file>
@@ -450,7 +453,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -743,13 +746,6 @@
       <sz val="10"/>
       <name val="Arial1"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -1460,7 +1456,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1616,9 +1612,6 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1669,7 +1662,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1754,11 +1750,7 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="43" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="43" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2226,68 +2218,68 @@
       <c r="D3" s="78"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="153" t="s">
+      <c r="A4" s="155" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="153"/>
+      <c r="B4" s="155"/>
       <c r="C4" s="79"/>
       <c r="D4" s="79"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="153"/>
-      <c r="B5" s="153"/>
+      <c r="A5" s="155"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="79"/>
       <c r="D5" s="79"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="153"/>
-      <c r="B6" s="153"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="155"/>
       <c r="C6" s="79"/>
       <c r="D6" s="79"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="153"/>
-      <c r="B7" s="153"/>
+      <c r="A7" s="155"/>
+      <c r="B7" s="155"/>
       <c r="C7" s="79"/>
       <c r="D7" s="79"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="161" t="s">
+      <c r="B9" s="163" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="161"/>
+      <c r="B10" s="163"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="161"/>
+      <c r="B11" s="163"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="156" t="s">
+      <c r="A14" s="158" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="156"/>
+      <c r="B14" s="158"/>
+      <c r="C14" s="158"/>
+      <c r="D14" s="158"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="156"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156"/>
+      <c r="A15" s="158"/>
+      <c r="B15" s="158"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="156"/>
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
+      <c r="A16" s="158"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="156"/>
-      <c r="B17" s="156"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
+      <c r="A17" s="158"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="158"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
@@ -2318,16 +2310,16 @@
       <c r="B23" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="183">
+      <c r="C23" s="153">
         <v>192000</v>
       </c>
       <c r="D23" s="54"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="120"/>
+      <c r="B24" s="119"/>
       <c r="C24" s="76">
         <f>SUM(C23:C23)</f>
         <v>192000</v>
@@ -2359,10 +2351,10 @@
       <c r="D28" s="80"/>
     </row>
     <row r="29" spans="1:7" hidden="1">
-      <c r="A29" s="120" t="s">
+      <c r="A29" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="121"/>
+      <c r="B29" s="120"/>
       <c r="C29" s="28">
         <f>SUM(C25:C28)</f>
         <v>0</v>
@@ -2395,7 +2387,7 @@
       <c r="A32" s="105" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="122"/>
+      <c r="B32" s="121"/>
       <c r="C32" s="91">
         <v>0</v>
       </c>
@@ -2423,11 +2415,11 @@
       <c r="D34" s="33"/>
     </row>
     <row r="35" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A35" s="154" t="s">
+      <c r="A35" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="155"/>
-      <c r="C35" s="181">
+      <c r="B35" s="157"/>
+      <c r="C35" s="154">
         <v>168183</v>
       </c>
       <c r="D35" s="88" t="s">
@@ -2449,7 +2441,7 @@
       <c r="A37" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="123"/>
+      <c r="B37" s="122"/>
       <c r="C37" s="20"/>
       <c r="D37" s="59"/>
     </row>
@@ -2498,7 +2490,7 @@
       <c r="A42" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="123"/>
+      <c r="B42" s="122"/>
       <c r="C42" s="21"/>
       <c r="D42" s="58">
         <f>SUM(C38:C41)</f>
@@ -2509,7 +2501,7 @@
       <c r="A43" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="123"/>
+      <c r="B43" s="122"/>
       <c r="C43" s="20"/>
       <c r="D43" s="59"/>
     </row>
@@ -2518,7 +2510,7 @@
         <v>96</v>
       </c>
       <c r="B44" s="54"/>
-      <c r="C44" s="152">
+      <c r="C44" s="94">
         <v>61000.42</v>
       </c>
       <c r="D44" s="86" t="s">
@@ -2530,419 +2522,419 @@
         <v>97</v>
       </c>
       <c r="B45" s="54"/>
-      <c r="C45" s="152">
-        <v>418590.24</v>
+      <c r="C45" s="94">
+        <v>396294.49</v>
       </c>
       <c r="D45" s="86" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A46" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="B46" s="54"/>
-      <c r="C46" s="152">
-        <v>396294.49</v>
-      </c>
-      <c r="D46" s="86" t="s">
         <v>119</v>
       </c>
+      <c r="F45" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A46" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="58">
+        <f>SUM(C44:C45)</f>
+        <v>457294.91</v>
+      </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="14" t="s">
-        <v>3</v>
+      <c r="A47" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="19"/>
-      <c r="D47" s="58">
-        <f>SUM(C44:C46)</f>
-        <v>875885.14999999991</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="61"/>
-    </row>
-    <row r="49" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A49" s="154" t="s">
+      <c r="D47" s="61"/>
+    </row>
+    <row r="48" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A48" s="156" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="155"/>
-      <c r="C49" s="152">
+      <c r="B48" s="157"/>
+      <c r="C48" s="94">
         <f>105000+3547.5</f>
         <v>108547.5</v>
       </c>
+      <c r="D48" s="84" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="30" customHeight="1">
+      <c r="A49" s="156" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" s="157"/>
+      <c r="C49" s="94">
+        <v>90000</v>
+      </c>
       <c r="D49" s="84" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="30" customHeight="1">
-      <c r="A50" s="154" t="s">
-        <v>123</v>
-      </c>
-      <c r="B50" s="155"/>
-      <c r="C50" s="152">
-        <v>90000</v>
+      <c r="A50" s="156" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" s="157"/>
+      <c r="C50" s="94">
+        <v>387000</v>
       </c>
       <c r="D50" s="84" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1">
-      <c r="A51" s="154" t="s">
-        <v>130</v>
-      </c>
-      <c r="B51" s="155"/>
-      <c r="C51" s="152">
-        <v>387000</v>
-      </c>
-      <c r="D51" s="84" t="s">
+    <row r="51" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A51" s="149" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" s="150"/>
+      <c r="C51" s="94">
+        <v>20000</v>
+      </c>
+      <c r="D51" s="84"/>
+    </row>
+    <row r="52" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A52" s="147" t="s">
+        <v>129</v>
+      </c>
+      <c r="B52" s="148"/>
+      <c r="C52" s="94">
+        <v>60000</v>
+      </c>
+      <c r="D52" s="84"/>
+    </row>
+    <row r="53" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A53" s="147" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="148"/>
+      <c r="C53" s="94">
+        <v>43200</v>
+      </c>
+      <c r="D53" s="84" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A54" s="149" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="150"/>
+      <c r="C54" s="94">
+        <v>36900</v>
+      </c>
+      <c r="D54" s="84" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A52" s="150" t="s">
-        <v>124</v>
-      </c>
-      <c r="B52" s="151"/>
-      <c r="C52" s="152">
-        <v>20000</v>
-      </c>
-      <c r="D52" s="84"/>
-    </row>
-    <row r="53" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A53" s="148" t="s">
-        <v>129</v>
-      </c>
-      <c r="B53" s="149"/>
-      <c r="C53" s="152">
-        <v>60000</v>
-      </c>
-      <c r="D53" s="84"/>
-    </row>
-    <row r="54" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A54" s="148" t="s">
-        <v>120</v>
-      </c>
-      <c r="B54" s="149"/>
-      <c r="C54" s="152">
-        <v>43200</v>
-      </c>
-      <c r="D54" s="84" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A55" s="150" t="s">
-        <v>120</v>
-      </c>
-      <c r="B55" s="151"/>
-      <c r="C55" s="152">
-        <v>36900</v>
-      </c>
-      <c r="D55" s="84" t="s">
-        <v>122</v>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A55" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="63">
+        <f>SUM(C48:C54)</f>
+        <v>745647.5</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="63">
-        <f>SUM(C49:C55)</f>
-        <v>745647.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="13" t="s">
+      <c r="A56" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B57" s="124"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="61"/>
+      <c r="B56" s="123"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="61"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="54"/>
+      <c r="C57" s="96"/>
+      <c r="D57" s="64"/>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="54" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="B58" s="54"/>
-      <c r="C58" s="96"/>
-      <c r="D58" s="64"/>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="54" t="s">
-        <v>104</v>
-      </c>
-      <c r="B59" s="54"/>
-      <c r="C59" s="94">
+      <c r="C58" s="94">
         <v>25055.13</v>
       </c>
-      <c r="D59" s="62"/>
+      <c r="D58" s="62"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A59" s="124" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" s="124"/>
+      <c r="C59" s="65"/>
+      <c r="D59" s="58">
+        <f>SUM(C57:C58)</f>
+        <v>25055.13</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="125" t="s">
-        <v>29</v>
-      </c>
-      <c r="B60" s="125"/>
-      <c r="C60" s="65"/>
-      <c r="D60" s="58">
-        <f>SUM(C58:C59)</f>
-        <v>25055.13</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="54"/>
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
-      <c r="D61" s="66"/>
-    </row>
-    <row r="62" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A62" s="158" t="s">
+      <c r="A60" s="54"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="66"/>
+    </row>
+    <row r="61" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A61" s="160" t="s">
         <v>117</v>
       </c>
-      <c r="B62" s="159"/>
-      <c r="C62" s="160"/>
-      <c r="D62" s="67">
-        <f>1955000-1644013.49</f>
-        <v>310986.51</v>
-      </c>
+      <c r="B61" s="161"/>
+      <c r="C61" s="162"/>
+      <c r="D61" s="67">
+        <f>1955000-1588180.54</f>
+        <v>366819.45999999996</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A62" s="125"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="68"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="24"/>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="126"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="68"/>
-      <c r="D63" s="69"/>
+      <c r="A63" s="126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" s="127"/>
+      <c r="C63" s="70"/>
+      <c r="D63" s="71">
+        <f>(SUM(D25:D61))</f>
+        <v>1954999.9999999998</v>
+      </c>
       <c r="E63" s="24"/>
-    </row>
-    <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="127" t="s">
-        <v>25</v>
-      </c>
-      <c r="B64" s="128"/>
-      <c r="C64" s="70"/>
-      <c r="D64" s="71">
-        <f>(SUM(D25:D62))</f>
-        <v>2317757.29</v>
-      </c>
-      <c r="E64" s="24"/>
-      <c r="F64" s="24"/>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="F63" s="24"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="68"/>
+      <c r="B64" s="68"/>
+      <c r="C64" s="68"/>
+      <c r="D64" s="68"/>
+      <c r="F64" s="83"/>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" thickBot="1">
       <c r="A65" s="68"/>
       <c r="B65" s="68"/>
       <c r="C65" s="68"/>
       <c r="D65" s="68"/>
-      <c r="F65" s="83"/>
-    </row>
-    <row r="66" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A66" s="68"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="68"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="129" t="s">
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="B67" s="130"/>
-      <c r="C67" s="72"/>
-      <c r="D67" s="73"/>
-    </row>
-    <row r="68" spans="1:6" ht="123.75" customHeight="1">
-      <c r="A68" s="154" t="s">
+      <c r="B66" s="129"/>
+      <c r="C66" s="72"/>
+      <c r="D66" s="73"/>
+    </row>
+    <row r="67" spans="1:4" ht="123.75" customHeight="1">
+      <c r="A67" s="156" t="s">
         <v>128</v>
       </c>
-      <c r="B68" s="155"/>
-      <c r="C68" s="152">
+      <c r="B67" s="157"/>
+      <c r="C67" s="94">
         <v>460000</v>
       </c>
-      <c r="D68" s="84"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="154" t="s">
+      <c r="D67" s="84"/>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="156" t="s">
         <v>126</v>
       </c>
-      <c r="B69" s="155"/>
-      <c r="C69" s="152">
+      <c r="B68" s="157"/>
+      <c r="C68" s="94">
         <v>105000</v>
       </c>
+      <c r="D68" s="60"/>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="132"/>
+      <c r="B69" s="133"/>
+      <c r="C69" s="94"/>
       <c r="D69" s="60"/>
     </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="133"/>
+    <row r="70" spans="1:4">
+      <c r="A70" s="124" t="s">
+        <v>29</v>
+      </c>
       <c r="B70" s="134"/>
-      <c r="C70" s="94"/>
-      <c r="D70" s="60"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="125" t="s">
-        <v>29</v>
-      </c>
-      <c r="B71" s="135"/>
-      <c r="C71" s="136"/>
-      <c r="D71" s="182">
-        <f>SUM(C68:C70)</f>
+      <c r="C70" s="135"/>
+      <c r="D70" s="151">
+        <f>SUM(C67:C69)</f>
         <v>565000</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15" customHeight="1">
+    <row r="71" spans="1:4" ht="15" customHeight="1">
+      <c r="A71" s="68"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="68"/>
+    </row>
+    <row r="72" spans="1:4" hidden="1">
       <c r="A72" s="68"/>
       <c r="B72" s="68"/>
       <c r="C72" s="68"/>
     </row>
-    <row r="73" spans="1:6" hidden="1">
-      <c r="A73" s="68"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="68"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="137" t="s">
+    <row r="73" spans="1:4">
+      <c r="A73" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="B74" s="137"/>
-      <c r="C74" s="138"/>
-      <c r="D74" s="90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A75" s="68"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="68"/>
-    </row>
-    <row r="76" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A76" s="127" t="s">
+      <c r="B73" s="136"/>
+      <c r="C73" s="137"/>
+      <c r="D73" s="90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A74" s="68"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="68"/>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A75" s="126" t="s">
         <v>36</v>
       </c>
-      <c r="B76" s="128"/>
-      <c r="C76" s="70"/>
-      <c r="D76" s="34">
-        <f>D71+D74</f>
+      <c r="B75" s="127"/>
+      <c r="C75" s="70"/>
+      <c r="D75" s="34">
+        <f>D70+D73</f>
         <v>565000</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A77" s="68"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="68"/>
-    </row>
-    <row r="78" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A78" s="139" t="s">
+    <row r="76" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A76" s="68"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="68"/>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A77" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="B78" s="140">
-        <f>D64</f>
-        <v>2317757.29</v>
-      </c>
-      <c r="C78" s="141"/>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A79" s="139" t="s">
+      <c r="B77" s="139">
+        <f>D63</f>
+        <v>1954999.9999999998</v>
+      </c>
+      <c r="C77" s="140"/>
+    </row>
+    <row r="78" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A78" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="B79" s="140">
-        <f>D64-D62</f>
-        <v>2006770.78</v>
+      <c r="B78" s="139">
+        <f>D63-D61</f>
+        <v>1588180.5399999998</v>
+      </c>
+      <c r="C78" s="68"/>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A79" s="138" t="s">
+        <v>37</v>
+      </c>
+      <c r="B79" s="139">
+        <f>D75-D73</f>
+        <v>565000</v>
       </c>
       <c r="C79" s="68"/>
     </row>
-    <row r="80" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A80" s="139" t="s">
-        <v>37</v>
-      </c>
-      <c r="B80" s="140">
-        <f>D76-D74</f>
+    <row r="80" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A80" s="138" t="s">
+        <v>52</v>
+      </c>
+      <c r="B80" s="139">
+        <f>D75</f>
         <v>565000</v>
       </c>
       <c r="C80" s="68"/>
     </row>
-    <row r="81" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A81" s="139" t="s">
-        <v>52</v>
-      </c>
-      <c r="B81" s="140">
-        <f>D76</f>
-        <v>565000</v>
-      </c>
+    <row r="81" spans="1:4">
+      <c r="A81" s="68"/>
+      <c r="B81" s="68"/>
       <c r="C81" s="68"/>
+      <c r="D81" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="68"/>
       <c r="B82" s="68"/>
       <c r="C82" s="68"/>
-      <c r="D82" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="68"/>
       <c r="B83" s="68"/>
       <c r="C83" s="68"/>
     </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="68"/>
-      <c r="B84" s="68"/>
+    <row r="84" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A84" s="141" t="s">
+        <v>47</v>
+      </c>
+      <c r="B84" s="142"/>
       <c r="C84" s="68"/>
     </row>
-    <row r="85" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A85" s="142" t="s">
-        <v>47</v>
-      </c>
-      <c r="B85" s="143"/>
+    <row r="85" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A85" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B85" s="143">
+        <v>464169.03999999957</v>
+      </c>
       <c r="C85" s="68"/>
     </row>
-    <row r="86" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A86" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B86" s="144">
-        <v>464169.03999999957</v>
+    <row r="86" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A86" s="144" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86" s="62">
+        <f>PRORRATEO!H24</f>
+        <v>2003283.8299999996</v>
       </c>
       <c r="C86" s="68"/>
     </row>
     <row r="87" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A87" s="145" t="s">
-        <v>55</v>
+      <c r="A87" s="144" t="s">
+        <v>54</v>
       </c>
       <c r="B87" s="62">
-        <f>PRORRATEO!H24</f>
-        <v>1942758.8299999996</v>
+        <f>B97</f>
+        <v>0</v>
       </c>
       <c r="C87" s="68"/>
     </row>
     <row r="88" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A88" s="145" t="s">
-        <v>54</v>
+      <c r="A88" s="144" t="s">
+        <v>134</v>
       </c>
       <c r="B88" s="62">
-        <f>B97</f>
-        <v>0</v>
+        <v>-60525</v>
       </c>
       <c r="C88" s="68"/>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="147" t="s">
+      <c r="A89" s="146" t="s">
         <v>38</v>
       </c>
       <c r="B89" s="62">
-        <f>-B79</f>
-        <v>-2006770.78</v>
+        <f>-B78</f>
+        <v>-1588180.5399999998</v>
       </c>
       <c r="C89" s="68"/>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="146" t="s">
+      <c r="A90" s="145" t="s">
         <v>39</v>
       </c>
       <c r="B90" s="62">
-        <f>-(B80)</f>
+        <f>-(B79)</f>
         <v>-565000</v>
       </c>
       <c r="C90" s="68"/>
@@ -2952,25 +2944,25 @@
         <v>11</v>
       </c>
       <c r="B91" s="106">
-        <f>SUM(B86:B90)</f>
-        <v>-164842.91000000085</v>
-      </c>
-      <c r="C91" s="132"/>
+        <f>SUM(B85:B90)</f>
+        <v>253747.32999999938</v>
+      </c>
+      <c r="C91" s="131"/>
     </row>
     <row r="92" spans="1:4" ht="34.5" customHeight="1">
       <c r="B92" s="22"/>
       <c r="C92" s="24"/>
-      <c r="D92" s="132"/>
+      <c r="D92" s="131"/>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="157" t="s">
+      <c r="A93" s="159" t="s">
         <v>46</v>
       </c>
-      <c r="B93" s="157"/>
+      <c r="B93" s="159"/>
     </row>
     <row r="94" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A94" s="157"/>
-      <c r="B94" s="157"/>
+      <c r="A94" s="159"/>
+      <c r="B94" s="159"/>
     </row>
     <row r="95" spans="1:4" ht="32.25" customHeight="1">
       <c r="A95" s="74"/>
@@ -2998,13 +2990,13 @@
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A93:B94"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3041,22 +3033,22 @@
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="107"/>
-      <c r="B1" s="166" t="str">
+      <c r="B1" s="168" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
       <c r="L1" s="108"/>
       <c r="M1" s="108"/>
       <c r="N1" s="108"/>
@@ -3065,16 +3057,16 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="110"/>
-      <c r="B2" s="167"/>
-      <c r="C2" s="167"/>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
-      <c r="F2" s="167"/>
-      <c r="G2" s="167"/>
-      <c r="H2" s="167"/>
-      <c r="I2" s="167"/>
-      <c r="J2" s="167"/>
-      <c r="K2" s="167"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
       <c r="L2" s="111"/>
       <c r="M2" s="111" t="s">
         <v>4</v>
@@ -3091,118 +3083,118 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="113"/>
-      <c r="B3" s="168"/>
-      <c r="C3" s="168"/>
-      <c r="D3" s="168"/>
-      <c r="E3" s="168"/>
-      <c r="F3" s="168"/>
-      <c r="G3" s="168"/>
-      <c r="H3" s="168"/>
-      <c r="I3" s="168"/>
-      <c r="J3" s="168"/>
-      <c r="K3" s="168"/>
+      <c r="B3" s="170"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="170"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="170"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="170"/>
+      <c r="I3" s="170"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="170"/>
       <c r="L3" s="114"/>
       <c r="M3" s="114" t="s">
         <v>56</v>
       </c>
       <c r="N3" s="115"/>
-      <c r="O3" s="119">
-        <v>0</v>
+      <c r="O3" s="183">
+        <v>565000</v>
       </c>
       <c r="P3" s="116"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="178" t="s">
+      <c r="B4" s="180" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="179"/>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="179"/>
-      <c r="G4" s="179"/>
-      <c r="H4" s="179"/>
-      <c r="I4" s="179"/>
-      <c r="J4" s="179"/>
-      <c r="K4" s="179"/>
-      <c r="L4" s="179"/>
-      <c r="M4" s="179"/>
-      <c r="N4" s="179"/>
-      <c r="O4" s="179"/>
-      <c r="P4" s="180"/>
+      <c r="C4" s="181"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="181"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="181"/>
+      <c r="H4" s="181"/>
+      <c r="I4" s="181"/>
+      <c r="J4" s="181"/>
+      <c r="K4" s="181"/>
+      <c r="L4" s="181"/>
+      <c r="M4" s="181"/>
+      <c r="N4" s="181"/>
+      <c r="O4" s="181"/>
+      <c r="P4" s="182"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="164" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="164" t="s">
+      <c r="B5" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="165" t="s">
+      <c r="C5" s="167" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="165" t="s">
+      <c r="D5" s="167" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="165" t="s">
+      <c r="E5" s="167" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="165" t="s">
+      <c r="F5" s="167" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="165" t="s">
+      <c r="G5" s="167" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="165" t="s">
+      <c r="H5" s="167" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="165" t="s">
+      <c r="I5" s="167" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="174" t="s">
+      <c r="J5" s="176" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="172" t="s">
+      <c r="K5" s="174" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="172" t="s">
+      <c r="L5" s="174" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="172" t="s">
+      <c r="M5" s="174" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="176" t="s">
+      <c r="N5" s="178" t="s">
         <v>51</v>
       </c>
       <c r="O5" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="169" t="s">
+      <c r="P5" s="171" t="s">
         <v>49</v>
       </c>
       <c r="S5" s="24"/>
       <c r="T5" s="22"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="163"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="165"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="171"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="165"/>
-      <c r="H6" s="165"/>
-      <c r="I6" s="171"/>
-      <c r="J6" s="175"/>
-      <c r="K6" s="173"/>
-      <c r="L6" s="172"/>
-      <c r="M6" s="173"/>
-      <c r="N6" s="177"/>
+      <c r="A6" s="165"/>
+      <c r="B6" s="166"/>
+      <c r="C6" s="167"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="167"/>
+      <c r="H6" s="167"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="177"/>
+      <c r="K6" s="175"/>
+      <c r="L6" s="174"/>
+      <c r="M6" s="175"/>
+      <c r="N6" s="179"/>
       <c r="O6" s="29" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="P6" s="169"/>
+      <c r="P6" s="171"/>
       <c r="S6" s="22">
         <v>65160</v>
       </c>
@@ -3246,7 +3238,7 @@
       </c>
       <c r="L7" s="40">
         <f>O$3*F7%</f>
-        <v>0</v>
+        <v>61358.999999999993</v>
       </c>
       <c r="M7" s="40">
         <f>O$2*F7%</f>
@@ -3257,11 +3249,11 @@
       </c>
       <c r="O7" s="42">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>4511743.01</v>
+        <v>4573102.01</v>
       </c>
       <c r="P7" s="43">
         <f t="shared" ref="P7:P23" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>4647095.01</v>
+        <v>4710295.01</v>
       </c>
       <c r="Q7" s="24">
         <v>0.01</v>
@@ -3297,7 +3289,7 @@
       <c r="G8" s="36">
         <v>440112.02</v>
       </c>
-      <c r="H8" s="184">
+      <c r="H8" s="37">
         <v>233588.14</v>
       </c>
       <c r="I8" s="38"/>
@@ -3311,7 +3303,7 @@
       </c>
       <c r="L8" s="40">
         <f t="shared" ref="L8:L23" si="4">O$3*F8%</f>
-        <v>0</v>
+        <v>63054</v>
       </c>
       <c r="M8" s="40">
         <f t="shared" ref="M8:M23" si="5">O$2*F8%</f>
@@ -3322,11 +3314,11 @@
       </c>
       <c r="O8" s="42">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>430898.02</v>
+        <v>493952.02</v>
       </c>
       <c r="P8" s="43">
         <f t="shared" si="0"/>
-        <v>443825.02</v>
+        <v>508771.02</v>
       </c>
       <c r="Q8" s="24">
         <f>Q7+0.01</f>
@@ -3380,7 +3372,7 @@
       </c>
       <c r="L9" s="101">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>39267.5</v>
       </c>
       <c r="M9" s="101">
         <f t="shared" si="5"/>
@@ -3391,11 +3383,11 @@
       </c>
       <c r="O9" s="103">
         <f t="shared" ref="O9:O23" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>461779.03</v>
+        <v>501046.03</v>
       </c>
       <c r="P9" s="104">
         <f t="shared" si="0"/>
-        <v>475632.03</v>
+        <v>516077.03</v>
       </c>
       <c r="Q9" s="24">
         <f t="shared" ref="Q9:Q22" si="7">Q8+0.01</f>
@@ -3434,7 +3426,7 @@
       <c r="G10" s="36">
         <v>145871.04000000001</v>
       </c>
-      <c r="H10" s="184">
+      <c r="H10" s="37">
         <f>-H20+158000</f>
         <v>147833.85999999999</v>
       </c>
@@ -3449,7 +3441,7 @@
       </c>
       <c r="L10" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>41640.5</v>
       </c>
       <c r="M10" s="40">
         <f t="shared" si="5"/>
@@ -3460,11 +3452,11 @@
       </c>
       <c r="O10" s="42">
         <f t="shared" si="6"/>
-        <v>142121.04</v>
+        <v>183761.04</v>
       </c>
       <c r="P10" s="43">
         <f t="shared" si="0"/>
-        <v>146385.04</v>
+        <v>189274.04</v>
       </c>
       <c r="Q10" s="24">
         <f t="shared" si="7"/>
@@ -3503,7 +3495,7 @@
       <c r="G11" s="36">
         <v>215058.05</v>
       </c>
-      <c r="H11" s="184">
+      <c r="H11" s="37">
         <f>G11</f>
         <v>215058.05</v>
       </c>
@@ -3518,7 +3510,7 @@
       </c>
       <c r="L11" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>60341.999999999993</v>
       </c>
       <c r="M11" s="40">
         <f t="shared" si="5"/>
@@ -3529,11 +3521,11 @@
       </c>
       <c r="O11" s="42">
         <f t="shared" si="6"/>
-        <v>208794.05</v>
+        <v>269136.05</v>
       </c>
       <c r="P11" s="43">
         <f t="shared" si="0"/>
-        <v>215058.05</v>
+        <v>277210.05</v>
       </c>
       <c r="Q11" s="24">
         <f t="shared" si="7"/>
@@ -3572,7 +3564,7 @@
       <c r="G12" s="36">
         <v>123762.06</v>
       </c>
-      <c r="H12" s="184">
+      <c r="H12" s="37">
         <f>145825-H22</f>
         <v>123762.84</v>
       </c>
@@ -3587,22 +3579,22 @@
       </c>
       <c r="L12" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>39267.5</v>
       </c>
       <c r="M12" s="40">
         <f t="shared" si="5"/>
         <v>135872.5</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="130">
         <v>0</v>
       </c>
       <c r="O12" s="42">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>135872.06</v>
+        <v>175139.06</v>
       </c>
       <c r="P12" s="43">
         <f t="shared" si="0"/>
-        <v>139948.06</v>
+        <v>180393.06</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="7"/>
@@ -3641,7 +3633,7 @@
       <c r="G13" s="36">
         <v>134700.07</v>
       </c>
-      <c r="H13" s="184">
+      <c r="H13" s="37">
         <f>G13</f>
         <v>134700.07</v>
       </c>
@@ -3656,7 +3648,7 @@
       </c>
       <c r="L13" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>38928.5</v>
       </c>
       <c r="M13" s="40">
         <f t="shared" si="5"/>
@@ -3667,11 +3659,11 @@
       </c>
       <c r="O13" s="42">
         <f t="shared" si="6"/>
-        <v>134700.07</v>
+        <v>173628.07</v>
       </c>
       <c r="P13" s="43">
         <f t="shared" si="0"/>
-        <v>138741.07</v>
+        <v>178837.07</v>
       </c>
       <c r="Q13" s="24">
         <f t="shared" si="7"/>
@@ -3711,7 +3703,7 @@
       <c r="G14" s="36">
         <v>202434.08</v>
       </c>
-      <c r="H14" s="184">
+      <c r="H14" s="37">
         <f>G14</f>
         <v>202434.08</v>
       </c>
@@ -3726,7 +3718,7 @@
       </c>
       <c r="L14" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>60341.999999999993</v>
       </c>
       <c r="M14" s="40">
         <f t="shared" si="5"/>
@@ -3737,11 +3729,11 @@
       </c>
       <c r="O14" s="42">
         <f t="shared" si="6"/>
-        <v>208794.08</v>
+        <v>269136.08</v>
       </c>
       <c r="P14" s="43">
         <f t="shared" si="0"/>
-        <v>215058.08</v>
+        <v>277210.08</v>
       </c>
       <c r="Q14" s="24">
         <f t="shared" si="7"/>
@@ -3780,21 +3772,21 @@
       <c r="G15" s="37">
         <v>526398.09</v>
       </c>
-      <c r="H15" s="185">
-        <f>135873+330000</f>
-        <v>465873</v>
+      <c r="H15" s="152">
+        <f>135873+330000+60525</f>
+        <v>526398</v>
       </c>
       <c r="I15" s="38"/>
       <c r="J15" s="100">
         <f t="shared" si="2"/>
-        <v>60525.089999999967</v>
+        <v>8.999999996740371E-2</v>
       </c>
       <c r="K15" s="100">
         <v>0</v>
       </c>
       <c r="L15" s="101">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>39267.5</v>
       </c>
       <c r="M15" s="101">
         <f t="shared" si="5"/>
@@ -3805,11 +3797,11 @@
       </c>
       <c r="O15" s="103">
         <f t="shared" si="6"/>
-        <v>196398.09</v>
+        <v>175140.09</v>
       </c>
       <c r="P15" s="104">
         <f t="shared" si="0"/>
-        <v>202290.09</v>
+        <v>180394.09</v>
       </c>
       <c r="Q15" s="24">
         <f t="shared" si="7"/>
@@ -3848,7 +3840,7 @@
       <c r="G16" s="36">
         <v>134700.1</v>
       </c>
-      <c r="H16" s="184">
+      <c r="H16" s="37">
         <f>134700.1</f>
         <v>134700.1</v>
       </c>
@@ -3863,7 +3855,7 @@
       </c>
       <c r="L16" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>38928.5</v>
       </c>
       <c r="M16" s="40">
         <f t="shared" si="5"/>
@@ -3874,11 +3866,11 @@
       </c>
       <c r="O16" s="42">
         <f t="shared" si="6"/>
-        <v>134700.1</v>
+        <v>173628.1</v>
       </c>
       <c r="P16" s="43">
         <f t="shared" si="0"/>
-        <v>138741.1</v>
+        <v>178837.1</v>
       </c>
       <c r="Q16" s="24">
         <f t="shared" si="7"/>
@@ -3918,7 +3910,7 @@
       <c r="G17" s="36">
         <v>222193.11</v>
       </c>
-      <c r="H17" s="184">
+      <c r="H17" s="37">
         <f>232254.11-H21+10166.15</f>
         <v>221892.11</v>
       </c>
@@ -3933,7 +3925,7 @@
       </c>
       <c r="L17" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>67122</v>
       </c>
       <c r="M17" s="40">
         <f t="shared" si="5"/>
@@ -3944,11 +3936,11 @@
       </c>
       <c r="O17" s="42">
         <f t="shared" si="6"/>
-        <v>232564.11</v>
+        <v>299686.11</v>
       </c>
       <c r="P17" s="43">
         <f t="shared" si="0"/>
-        <v>239541.11</v>
+        <v>308677.11</v>
       </c>
       <c r="Q17" s="24">
         <f t="shared" si="7"/>
@@ -4002,7 +3994,7 @@
       </c>
       <c r="L18" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3220.4999999999995</v>
       </c>
       <c r="M18" s="40">
         <f t="shared" si="5"/>
@@ -4013,11 +4005,11 @@
       </c>
       <c r="O18" s="42">
         <f t="shared" si="6"/>
-        <v>34626.120000000003</v>
+        <v>37846.120000000003</v>
       </c>
       <c r="P18" s="43">
         <f t="shared" si="0"/>
-        <v>35665.120000000003</v>
+        <v>38981.120000000003</v>
       </c>
       <c r="Q18" s="24">
         <f t="shared" si="7"/>
@@ -4054,7 +4046,7 @@
       <c r="G19" s="36">
         <v>9864.1299999999992</v>
       </c>
-      <c r="H19" s="184">
+      <c r="H19" s="37">
         <v>10160.129999999999</v>
       </c>
       <c r="I19" s="38"/>
@@ -4068,7 +4060,7 @@
       </c>
       <c r="L19" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2938</v>
       </c>
       <c r="M19" s="40">
         <f t="shared" si="5"/>
@@ -4079,11 +4071,11 @@
       </c>
       <c r="O19" s="42">
         <f t="shared" si="6"/>
-        <v>9870.1299999999992</v>
+        <v>12808.13</v>
       </c>
       <c r="P19" s="43">
         <f t="shared" si="0"/>
-        <v>10166.129999999999</v>
+        <v>13192.13</v>
       </c>
       <c r="Q19" s="24">
         <f t="shared" si="7"/>
@@ -4122,7 +4114,7 @@
       <c r="G20" s="36">
         <v>10166.14</v>
       </c>
-      <c r="H20" s="184">
+      <c r="H20" s="37">
         <f>G20</f>
         <v>10166.14</v>
       </c>
@@ -4137,7 +4129,7 @@
       </c>
       <c r="L20" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2938</v>
       </c>
       <c r="M20" s="40">
         <f t="shared" si="5"/>
@@ -4148,11 +4140,11 @@
       </c>
       <c r="O20" s="42">
         <f t="shared" si="6"/>
-        <v>10166.14</v>
+        <v>13104.14</v>
       </c>
       <c r="P20" s="43">
         <f t="shared" si="0"/>
-        <v>10471.14</v>
+        <v>13497.14</v>
       </c>
       <c r="Q20" s="24">
         <f t="shared" si="7"/>
@@ -4189,7 +4181,7 @@
       <c r="G21" s="36">
         <v>20528.150000000001</v>
       </c>
-      <c r="H21" s="184">
+      <c r="H21" s="37">
         <f>G21</f>
         <v>20528.150000000001</v>
       </c>
@@ -4204,7 +4196,7 @@
       </c>
       <c r="L21" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2938</v>
       </c>
       <c r="M21" s="40">
         <f t="shared" si="5"/>
@@ -4215,11 +4207,11 @@
       </c>
       <c r="O21" s="42">
         <f t="shared" si="6"/>
-        <v>10166.15</v>
+        <v>13104.15</v>
       </c>
       <c r="P21" s="43">
         <f t="shared" si="0"/>
-        <v>10471.15</v>
+        <v>13497.15</v>
       </c>
       <c r="Q21" s="24">
         <f t="shared" si="7"/>
@@ -4256,7 +4248,7 @@
       <c r="G22" s="36">
         <v>22062.16</v>
       </c>
-      <c r="H22" s="184">
+      <c r="H22" s="37">
         <f>G22</f>
         <v>22062.16</v>
       </c>
@@ -4271,7 +4263,7 @@
       </c>
       <c r="L22" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3446.4999999999995</v>
       </c>
       <c r="M22" s="40">
         <f t="shared" si="5"/>
@@ -4282,11 +4274,11 @@
       </c>
       <c r="O22" s="42">
         <f t="shared" si="6"/>
-        <v>11926.16</v>
+        <v>15372.16</v>
       </c>
       <c r="P22" s="43">
         <f t="shared" si="0"/>
-        <v>12284.16</v>
+        <v>15833.16</v>
       </c>
       <c r="Q22" s="24">
         <f t="shared" si="7"/>
@@ -4355,7 +4347,7 @@
       </c>
       <c r="H24" s="30">
         <f>SUM(H7:H23)</f>
-        <v>1942758.8299999996</v>
+        <v>2003283.8299999996</v>
       </c>
       <c r="I24" s="30">
         <f>SUM(I7:I23)</f>
@@ -4365,7 +4357,7 @@
       <c r="K24" s="30"/>
       <c r="L24" s="30">
         <f>SUM(L7:L23)</f>
-        <v>0</v>
+        <v>565000</v>
       </c>
       <c r="M24" s="30">
         <f>SUM(M7:M23)</f>
@@ -4377,11 +4369,11 @@
       </c>
       <c r="O24" s="53">
         <f>SUM(O7:O22)</f>
-        <v>6875118.3599999994</v>
+        <v>7379589.3599999994</v>
       </c>
       <c r="P24" s="53">
         <f>SUM(P7:P22)</f>
-        <v>7081372.3599999994</v>
+        <v>7600976.3599999994</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="12.75" customHeight="1">
@@ -4391,91 +4383,91 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="D27" s="170" t="s">
+      <c r="D27" s="172" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="170"/>
-      <c r="F27" s="170"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="170"/>
-      <c r="I27" s="170"/>
-      <c r="J27" s="170"/>
-      <c r="K27" s="170"/>
-      <c r="L27" s="170"/>
-      <c r="M27" s="170"/>
-      <c r="N27" s="170"/>
-      <c r="O27" s="170"/>
+      <c r="E27" s="172"/>
+      <c r="F27" s="172"/>
+      <c r="G27" s="172"/>
+      <c r="H27" s="172"/>
+      <c r="I27" s="172"/>
+      <c r="J27" s="172"/>
+      <c r="K27" s="172"/>
+      <c r="L27" s="172"/>
+      <c r="M27" s="172"/>
+      <c r="N27" s="172"/>
+      <c r="O27" s="172"/>
       <c r="S27" s="22"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="170"/>
-      <c r="E28" s="170"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="170"/>
-      <c r="H28" s="170"/>
-      <c r="I28" s="170"/>
-      <c r="J28" s="170"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="170"/>
-      <c r="M28" s="170"/>
-      <c r="N28" s="170"/>
-      <c r="O28" s="170"/>
+      <c r="D28" s="172"/>
+      <c r="E28" s="172"/>
+      <c r="F28" s="172"/>
+      <c r="G28" s="172"/>
+      <c r="H28" s="172"/>
+      <c r="I28" s="172"/>
+      <c r="J28" s="172"/>
+      <c r="K28" s="172"/>
+      <c r="L28" s="172"/>
+      <c r="M28" s="172"/>
+      <c r="N28" s="172"/>
+      <c r="O28" s="172"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="170"/>
-      <c r="E29" s="170"/>
-      <c r="F29" s="170"/>
-      <c r="G29" s="170"/>
-      <c r="H29" s="170"/>
-      <c r="I29" s="170"/>
-      <c r="J29" s="170"/>
-      <c r="K29" s="170"/>
-      <c r="L29" s="170"/>
-      <c r="M29" s="170"/>
-      <c r="N29" s="170"/>
-      <c r="O29" s="170"/>
+      <c r="D29" s="172"/>
+      <c r="E29" s="172"/>
+      <c r="F29" s="172"/>
+      <c r="G29" s="172"/>
+      <c r="H29" s="172"/>
+      <c r="I29" s="172"/>
+      <c r="J29" s="172"/>
+      <c r="K29" s="172"/>
+      <c r="L29" s="172"/>
+      <c r="M29" s="172"/>
+      <c r="N29" s="172"/>
+      <c r="O29" s="172"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="170"/>
-      <c r="E30" s="170"/>
-      <c r="F30" s="170"/>
-      <c r="G30" s="170"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="170"/>
-      <c r="J30" s="170"/>
-      <c r="K30" s="170"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="170"/>
-      <c r="O30" s="170"/>
+      <c r="D30" s="172"/>
+      <c r="E30" s="172"/>
+      <c r="F30" s="172"/>
+      <c r="G30" s="172"/>
+      <c r="H30" s="172"/>
+      <c r="I30" s="172"/>
+      <c r="J30" s="172"/>
+      <c r="K30" s="172"/>
+      <c r="L30" s="172"/>
+      <c r="M30" s="172"/>
+      <c r="N30" s="172"/>
+      <c r="O30" s="172"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="170"/>
-      <c r="E31" s="170"/>
-      <c r="F31" s="170"/>
-      <c r="G31" s="170"/>
-      <c r="H31" s="170"/>
-      <c r="I31" s="170"/>
-      <c r="J31" s="170"/>
-      <c r="K31" s="170"/>
-      <c r="L31" s="170"/>
-      <c r="M31" s="170"/>
-      <c r="N31" s="170"/>
-      <c r="O31" s="170"/>
+      <c r="D31" s="172"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="172"/>
+      <c r="G31" s="172"/>
+      <c r="H31" s="172"/>
+      <c r="I31" s="172"/>
+      <c r="J31" s="172"/>
+      <c r="K31" s="172"/>
+      <c r="L31" s="172"/>
+      <c r="M31" s="172"/>
+      <c r="N31" s="172"/>
+      <c r="O31" s="172"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="170"/>
-      <c r="E32" s="170"/>
-      <c r="F32" s="170"/>
-      <c r="G32" s="170"/>
-      <c r="H32" s="170"/>
-      <c r="I32" s="170"/>
-      <c r="J32" s="170"/>
-      <c r="K32" s="170"/>
-      <c r="L32" s="170"/>
-      <c r="M32" s="170"/>
-      <c r="N32" s="170"/>
-      <c r="O32" s="170"/>
+      <c r="D32" s="172"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="172"/>
+      <c r="G32" s="172"/>
+      <c r="H32" s="172"/>
+      <c r="I32" s="172"/>
+      <c r="J32" s="172"/>
+      <c r="K32" s="172"/>
+      <c r="L32" s="172"/>
+      <c r="M32" s="172"/>
+      <c r="N32" s="172"/>
+      <c r="O32" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="18">
